--- a/RXL_TextBetween.xlsx
+++ b/RXL_TextBetween.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\_RXL\Development\LAMBDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\_RXL\Development\LAMBDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B480AF-58A7-4284-BDEB-8E2AAAA1A084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FBA08B-2CCD-4D1D-BB98-C1EFC14B31E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29E0D24-0EA8-4D41-8E06-9F040E158B6C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C29E0D24-0EA8-4D41-8E06-9F040E158B6C}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBetween" sheetId="13" r:id="rId1"/>
     <sheet name="Demo" sheetId="14" r:id="rId2"/>
-    <sheet name="Lookups" sheetId="12" r:id="rId3"/>
+    <sheet name="VBA" sheetId="15" r:id="rId3"/>
+    <sheet name="Lookups" sheetId="12" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_OnOff">Lookups!$C$6:$C$7</definedName>
     <definedName name="_YesNo">Lookups!$C$3:$C$4</definedName>
-    <definedName name="RXL_TextBetween" comment="Returns the characters from a text string between a starting delimiter character(s) and ending delimiter character(s)">_xlfn.LAMBDA(_xlpm.text,_xlop.start_delimiter,_xlop.end_delimiter,_xlop.start_instance,_xlop.end_instance,_xlop.case_sensitive,_xlop.if_not_found,_xlfn.LET(_xlpm._delimA,IF(OR(_xlfn.ISOMITTED(_xlpm.start_delimiter),ISBLANK(_xlpm.start_delimiter)),"",_xlpm.start_delimiter),_xlpm._delimB,IF(OR(_xlfn.ISOMITTED(_xlpm.end_delimiter),ISBLANK(_xlpm.end_delimiter)),"",_xlpm.end_delimiter),_xlpm._instA,IF(OR(_xlfn.ISOMITTED(_xlpm.start_instance),ISBLANK(_xlpm.start_instance)),1,INT(_xlpm.start_instance)),_xlpm._instB,IF(OR(_xlfn.ISOMITTED(_xlpm.end_instance),ISBLANK(_xlpm.end_instance)),-1,INT(_xlpm.end_instance)),_xlpm._case,IF(_xlfn.ISOMITTED(_xlpm.case_sensitive),0,IF(_xlpm.case_sensitive,0,1)),_xlpm._inf,IF(OR(_xlfn.ISOMITTED(_xlpm.if_not_found),ISBLANK(_xlpm.if_not_found),_xlpm.if_not_found="",AND(ISLOGICAL(_xlpm.if_not_found),_xlpm.if_not_found=FALSE)),NA(),IF(ISLOGICAL(_xlpm.if_not_found),_xlpm.text,_xlpm.if_not_found)),_xlpm._end,IF(ISLOGICAL(_xlpm.if_not_found),_xlpm.if_not_found*1,0),_xlpm._inpChk,IF(OR(NOT(ISNUMBER(_xlpm._instA)),NOT(ISNUMBER(_xlpm._instB)),AND(NOT(ISLOGICAL(_xlpm._case)),NOT(ISNUMBER(_xlpm._case)))),2,1),_xlpm._calc,IF(OR(AND(_xlpm._delimA="",_xlpm._delimB="")),_xlpm.text,_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.text,_xlpm._delimA,_xlpm._instA,_xlpm._case,_xlpm._end,_xlpm._inf),_xlpm._delimB,_xlpm._instB,_xlpm._case,,_xlpm._inf)),_xlpm._rtn,IF(AND(ISERROR(_xlpm._calc),_xlpm._end=1),_xlpm.text,_xlpm._calc),CHOOSE(_xlpm._inpChk,_xlpm._rtn,#VALUE!)))</definedName>
+    <definedName name="RXL_TextBetween" comment="Returns the characters from a text string between a starting delimiter character(s) and ending delimiter character(s)">_xlfn.LAMBDA(_xlpm.text,_xlop.start_delimiter,_xlop.end_delimiter,_xlop.start_instance,_xlop.end_instance,_xlop.case_sensitive,_xlop.if_not_found, _xlfn.LET(_xlpm._delimA, IF(OR(_xlfn.ISOMITTED(_xlpm.start_delimiter), ISBLANK(_xlpm.start_delimiter)), "", _xlpm.start_delimiter), _xlpm._delimB, IF(OR(_xlfn.ISOMITTED(_xlpm.end_delimiter), ISBLANK(_xlpm.end_delimiter)), "", _xlpm.end_delimiter), _xlpm._instA, IF(OR(_xlfn.ISOMITTED(_xlpm.start_instance), ISBLANK(_xlpm.start_instance)), 1, INT(_xlpm.start_instance)), _xlpm._instB, IF(OR(_xlfn.ISOMITTED(_xlpm.end_instance), ISBLANK(_xlpm.end_instance)), -1, INT(_xlpm.end_instance)), _xlpm._case, IF(_xlfn.ISOMITTED(_xlpm.case_sensitive), 0, IF(_xlpm.case_sensitive, 0, 1)), _xlpm._inf, IF(OR(_xlfn.ISOMITTED(_xlpm.if_not_found), ISBLANK(_xlpm.if_not_found), _xlpm.if_not_found = "", AND(ISLOGICAL(_xlpm.if_not_found), _xlpm.if_not_found = FALSE)), NA(), IF(ISLOGICAL(_xlpm.if_not_found), _xlpm.text, _xlpm.if_not_found)), _xlpm._end, IF(ISLOGICAL(_xlpm.if_not_found), _xlpm.if_not_found * 1, 0), _xlpm._inpChk, IF(OR(NOT(ISNUMBER(_xlpm._instA)), _xlpm._instA = 0, NOT(ISNUMBER(_xlpm._instB)), _xlpm._instB = 0, AND(NOT(ISLOGICAL(_xlpm._case)), NOT(ISNUMBER(_xlpm._case)))), 2, 1), _xlpm._calc, IF(OR(AND(_xlpm._delimA = "", _xlpm._delimB = "")), _xlpm.text, _xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.text, _xlpm._delimA, _xlpm._instA, _xlpm._case, _xlpm._end, _xlpm._inf), _xlpm._delimB, _xlpm._instB, _xlpm._case, , _xlpm._inf)), _xlpm._rtn, IF(AND(ISERROR(_xlpm._calc), _xlpm._end = 1), _xlpm.text, _xlpm._calc), CHOOSE(_xlpm._inpChk, _xlpm._rtn, #VALUE!)))</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="autoNoTable"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="229">
   <si>
     <t>)</t>
   </si>
@@ -2225,6 +2226,556 @@
   </si>
   <si>
     <t>https://gist.github.com/r-silk/b33b16e634e1ff6aa054cd6149964d80</t>
+  </si>
+  <si>
+    <t>VBA Code</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>A.</t>
+  </si>
+  <si>
+    <t>Start by ensuring that you have this Workbook and the Workbook you wish to copy the function to open in the same Excel instance</t>
+  </si>
+  <si>
+    <t>B.</t>
+  </si>
+  <si>
+    <t>Open the VB Editor window</t>
+  </si>
+  <si>
+    <t>C.</t>
+  </si>
+  <si>
+    <t>D.</t>
+  </si>
+  <si>
+    <t>In the code window which opens for ThisWorkbook, paste the VBA code from below exactly as written</t>
+  </si>
+  <si>
+    <t>E.</t>
+  </si>
+  <si>
+    <t>After copying the VBA code into code window, update line 11 replacing the text "Example.xlsx" with the name of your Excel Workbook/file</t>
+  </si>
+  <si>
+    <t>F.</t>
+  </si>
+  <si>
+    <t>Run the CopyLambda sub routine in ThisWorkbook module and check the Immediate window for the feedback message</t>
+  </si>
+  <si>
+    <t>In order to copy across the RXL_TextBetween() function from this Workbook to your own project you can use the instructions and VBA code below .</t>
+  </si>
+  <si>
+    <t>In the VB Editor Project Explorer window, select this Workbook (RXL_TextBetween.xlsx) and double click on the object named "ThisWorkbook"</t>
+  </si>
+  <si>
+    <t>Also check line 7 of the code has the correct name of the function you wish to copy (i.e. "RXL_TextBetween")</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Private Sub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CopyLambda()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Workbook, nm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Name, fn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> strLambda </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As String</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    'Name of custom Lambda function to copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    On Error Resume Next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        'Update "Example.xlsx" with name of the Workbook you wish to copy the function to</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb = Application.Workbooks("Example.xlsx")</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    On Error GoTo 0</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is Nothing Then</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        Exit Sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    End If</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> nm = ThisWorkbook.Names(strLambda)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If Not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> nm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is Nothing Then</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        Err.Clear</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> fn = wb.Names.Add(Name:=nm.Name, _</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                              RefersTo:=nm.RefersTo, _</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                              Visible:=nm.Visible)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Err.Number = 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Then</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">            fn.Comment = nm.Comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        End If</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Else</t>
+  </si>
+  <si>
+    <t>End Sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    strLambda = "RXL_TextBetween"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: Destination Workbook not found - please ensure it is open"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "Success! -&gt; " &amp; strLambda &amp; " copied to " &amp; wb.Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: Unable to copy " &amp; strLambda &amp; " to " &amp; wb.Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: " &amp; strLambda &amp; " not found"</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2241,7 +2792,7 @@
     <numFmt numFmtId="170" formatCode="&quot;On (1)&quot;;[Red]&quot;Err&quot;;&quot;Off (0)&quot;"/>
     <numFmt numFmtId="171" formatCode="&quot;Yes (1)&quot;;[Red]&quot;Err&quot;;&quot;No (0)&quot;"/>
   </numFmts>
-  <fonts count="56" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF002138"/>
@@ -2649,6 +3200,17 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF002138"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="42">
@@ -3417,7 +3979,7 @@
     <xf numFmtId="166" fontId="13" fillId="40" borderId="11" applyNumberFormat="0"/>
     <xf numFmtId="0" fontId="52" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="171" fontId="16" fillId="32" borderId="10" xfId="59" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3533,6 +4095,9 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="30" xfId="49" applyBorder="1"/>
     <xf numFmtId="0" fontId="55" fillId="41" borderId="28" xfId="91" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="73"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="92">
     <cellStyle name="20% - Accent1" xfId="31" builtinId="30" customBuiltin="1"/>
@@ -3605,7 +4170,7 @@
     <cellStyle name="Output - SubTotal" xfId="68" xr:uid="{3944BA35-D861-48C8-BF5E-3B5A261E1A76}"/>
     <cellStyle name="Output - Text" xfId="69" xr:uid="{D8AED5B9-3D8F-49BF-8E7D-B2C435B0B345}"/>
     <cellStyle name="Output - Total" xfId="70" xr:uid="{4535EB24-0E67-4CEB-99CB-25A662CC9E57}"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Per cent" xfId="5" builtinId="5" customBuiltin="1"/>
     <cellStyle name="Ref.In - #" xfId="78" xr:uid="{7AC7FA44-CE33-4D97-A9FF-6DB2BE2FBF7C}"/>
     <cellStyle name="Ref.In - %" xfId="79" xr:uid="{BE627C07-1DF5-42CE-90A7-95B617354C42}"/>
     <cellStyle name="Ref.In - Date" xfId="80" xr:uid="{70FB18BE-2731-4B77-8479-BF1A1A35C14E}"/>
@@ -3763,6 +4328,237 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>355542</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="A black and white logo&#10;&#10;AI-generated content may be incorrect.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E071BA9-EA1F-4829-AF3A-C8478F85A089}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="38100"/>
+          <a:ext cx="609600" cy="317442"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>549110</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>58034</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8A12FEA-3432-EE19-13C6-4EBD15773D42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="1508760"/>
+          <a:ext cx="5425910" cy="1414394"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>526364</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>23322</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{778C5660-5799-9A50-E18D-E259920777ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="3261360"/>
+          <a:ext cx="4183964" cy="3307542"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>450919</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>15774</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A6D5614-6020-FD57-7377-C0660FC8E9B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="7292340"/>
+          <a:ext cx="9594919" cy="3825774"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>175645</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>53417</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA061A14-E593-3326-5964-4DA5A0600114}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="11490960"/>
+          <a:ext cx="4442845" cy="891617"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4089,7 +4885,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="976" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="9">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -4121,20 +4917,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7340545-A130-4DC7-ACDB-2FCDAA37438B}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S211"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="1" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19"/>
       <c r="C1" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B3" s="40" t="s">
         <v>12</v>
       </c>
@@ -4156,37 +4953,37 @@
       <c r="R3" s="24"/>
       <c r="S3" s="24"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D7" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D8" s="20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C10" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D11" s="21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D13" s="22" t="s">
         <v>19</v>
       </c>
@@ -4194,19 +4991,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D14" s="22"/>
       <c r="F14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D15" s="22"/>
       <c r="F15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D16" s="22" t="s">
         <v>22</v>
       </c>
@@ -4214,7 +5011,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D17" s="22" t="s">
         <v>23</v>
       </c>
@@ -4222,19 +5019,19 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D18" s="22"/>
       <c r="F18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D19" s="22"/>
       <c r="F19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D20" s="22" t="s">
         <v>26</v>
       </c>
@@ -4242,7 +5039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D21" s="22"/>
       <c r="F21" s="25">
         <v>0</v>
@@ -4251,7 +5048,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D22" s="22"/>
       <c r="F22" s="25">
         <v>1</v>
@@ -4260,7 +5057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D23" s="22" t="s">
         <v>29</v>
       </c>
@@ -4268,7 +5065,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D24" s="22"/>
       <c r="F24" s="25">
         <v>0</v>
@@ -4277,7 +5074,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D25" s="22"/>
       <c r="F25" s="25">
         <v>1</v>
@@ -4286,7 +5083,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D26" s="22" t="s">
         <v>32</v>
       </c>
@@ -4294,17 +5091,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C28" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D29" s="23" t="e">
         <v>#VALUE!</v>
       </c>
@@ -4312,7 +5109,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D30" s="23" t="e">
         <v>#N/A</v>
       </c>
@@ -4320,7 +5117,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D31" s="23" t="e">
         <v>#N/A</v>
       </c>
@@ -4328,7 +5125,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34" s="40" t="s">
         <v>44</v>
       </c>
@@ -4350,37 +5147,37 @@
       <c r="R34" s="24"/>
       <c r="S34" s="24"/>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D38" s="20" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D39" s="20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C41" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D42" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D44" s="22" t="s">
         <v>19</v>
       </c>
@@ -4388,19 +5185,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D45" s="22"/>
       <c r="F45" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D46" s="22"/>
       <c r="F46" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D47" s="22" t="s">
         <v>22</v>
       </c>
@@ -4408,7 +5205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D48" s="22" t="s">
         <v>23</v>
       </c>
@@ -4416,19 +5213,19 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D49" s="22"/>
       <c r="F49" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D50" s="22"/>
       <c r="F50" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D51" s="22" t="s">
         <v>26</v>
       </c>
@@ -4436,7 +5233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D52" s="22"/>
       <c r="F52" s="25">
         <v>0</v>
@@ -4445,7 +5242,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D53" s="22"/>
       <c r="F53" s="25">
         <v>1</v>
@@ -4454,7 +5251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D54" s="22" t="s">
         <v>29</v>
       </c>
@@ -4462,7 +5259,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D55" s="22"/>
       <c r="F55" s="25">
         <v>0</v>
@@ -4471,7 +5268,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D56" s="22"/>
       <c r="F56" s="25">
         <v>1</v>
@@ -4480,7 +5277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D57" s="22" t="s">
         <v>32</v>
       </c>
@@ -4488,17 +5285,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F58" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C59" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D60" s="23" t="e">
         <v>#VALUE!</v>
       </c>
@@ -4506,7 +5303,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D61" s="23" t="e">
         <v>#N/A</v>
       </c>
@@ -4514,7 +5311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D62" s="23" t="e">
         <v>#N/A</v>
       </c>
@@ -4522,7 +5319,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="2:8" s="13" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:8" s="13" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="14">
         <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
         <v>1</v>
@@ -4531,37 +5328,37 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C67" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C73" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C75" t="s">
         <v>118</v>
       </c>
@@ -4569,7 +5366,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D76" s="18" t="s">
         <v>55</v>
       </c>
@@ -4580,14 +5377,14 @@
       <c r="G76" s="28"/>
       <c r="H76" s="29"/>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D77" s="18" t="s">
         <v>57</v>
       </c>
       <c r="E77" s="30"/>
       <c r="F77" s="30"/>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D78" s="18" t="s">
         <v>58</v>
       </c>
@@ -4603,7 +5400,7 @@
       <c r="G78" s="10"/>
       <c r="H78" s="8"/>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="E79" s="4" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E78)</f>
         <v>= LAMBDA(text,start_delimiter,end_delimiter,
@@ -4613,7 +5410,7 @@
 ))(E76, E77, F77)</v>
       </c>
     </row>
-    <row r="81" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>119</v>
       </c>
@@ -4621,7 +5418,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="82" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D82" s="18" t="s">
         <v>55</v>
       </c>
@@ -4632,14 +5429,14 @@
       <c r="G82" s="28"/>
       <c r="H82" s="29"/>
     </row>
-    <row r="83" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D83" s="18" t="s">
         <v>57</v>
       </c>
       <c r="E83" s="30"/>
       <c r="F83" s="30"/>
     </row>
-    <row r="84" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D84" s="18" t="s">
         <v>58</v>
       </c>
@@ -4661,7 +5458,7 @@
       <c r="G84" s="10"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E85" s="4" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E84)</f>
         <v>= LAMBDA(text,[start_delimiter],[end_delimiter],
@@ -4677,7 +5474,7 @@
 )(E82, E83, F83)</v>
       </c>
     </row>
-    <row r="87" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
         <v>120</v>
       </c>
@@ -4685,7 +5482,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="88" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D88" s="18" t="s">
         <v>55</v>
       </c>
@@ -4696,7 +5493,7 @@
       <c r="G88" s="28"/>
       <c r="H88" s="29"/>
     </row>
-    <row r="89" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D89" s="18" t="s">
         <v>57</v>
       </c>
@@ -4707,7 +5504,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D90" s="18" t="s">
         <v>63</v>
       </c>
@@ -4718,7 +5515,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="91" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D91" s="18" t="s">
         <v>58</v>
       </c>
@@ -4747,7 +5544,7 @@
       <c r="G91" s="10"/>
       <c r="H91" s="8"/>
     </row>
-    <row r="92" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E92" s="4" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E91)</f>
         <v>= LAMBDA(text,[start_delimiter],[end_delimiter],[start_instance],[end_instance],
@@ -4770,7 +5567,7 @@
 )(E88, E89, F89, E90, F90)</v>
       </c>
     </row>
-    <row r="94" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
         <v>121</v>
       </c>
@@ -4778,7 +5575,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D95" s="18" t="s">
         <v>55</v>
       </c>
@@ -4789,7 +5586,7 @@
       <c r="G95" s="28"/>
       <c r="H95" s="29"/>
     </row>
-    <row r="96" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D96" s="18" t="s">
         <v>57</v>
       </c>
@@ -4800,7 +5597,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="97" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D97" s="18" t="s">
         <v>63</v>
       </c>
@@ -4811,7 +5608,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="98" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D98" s="18" t="s">
         <v>66</v>
       </c>
@@ -4819,7 +5616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D99" s="18" t="s">
         <v>58</v>
       </c>
@@ -4853,7 +5650,7 @@
       <c r="G99" s="10"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E100" s="4" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E99)</f>
         <v>= LAMBDA(text,[start_delimiter],[end_delimiter],[start_instance],[end_instance],[case_sensitive],
@@ -4881,7 +5678,7 @@
 )(E95, E96, F96, E97, F97, E98)</v>
       </c>
     </row>
-    <row r="102" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
         <v>122</v>
       </c>
@@ -4889,7 +5686,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D103" s="18" t="s">
         <v>55</v>
       </c>
@@ -4900,7 +5697,7 @@
       <c r="G103" s="28"/>
       <c r="H103" s="29"/>
     </row>
-    <row r="104" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D104" s="18" t="s">
         <v>57</v>
       </c>
@@ -4911,7 +5708,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="105" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D105" s="18" t="s">
         <v>63</v>
       </c>
@@ -4922,7 +5719,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="106" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D106" s="18" t="s">
         <v>66</v>
       </c>
@@ -4930,7 +5727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D107" s="18" t="s">
         <v>68</v>
       </c>
@@ -4939,7 +5736,7 @@
       </c>
       <c r="F107" s="29"/>
     </row>
-    <row r="108" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D108" s="18" t="s">
         <v>58</v>
       </c>
@@ -4978,7 +5775,7 @@
       <c r="G108" s="10"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="3:8" x14ac:dyDescent="0.3">
       <c r="E109" s="4" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E108)</f>
         <v>= LAMBDA(text,[start_delimiter],[end_delimiter],[start_instance],[end_instance],[case_sensitive],[if_not_found],
@@ -5011,7 +5808,7 @@
 )(E103, E104, F104, E105, F105, E106, E107)</v>
       </c>
     </row>
-    <row r="111" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C111" t="s">
         <v>123</v>
       </c>
@@ -5019,7 +5816,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D112" s="18" t="s">
         <v>55</v>
       </c>
@@ -5030,7 +5827,7 @@
       <c r="G112" s="28"/>
       <c r="H112" s="29"/>
     </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D113" s="18" t="s">
         <v>57</v>
       </c>
@@ -5041,7 +5838,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D114" s="18" t="s">
         <v>63</v>
       </c>
@@ -5052,7 +5849,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D115" s="18" t="s">
         <v>66</v>
       </c>
@@ -5060,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D116" s="18" t="s">
         <v>68</v>
       </c>
@@ -5069,7 +5866,7 @@
       </c>
       <c r="F116" s="29"/>
     </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D117" s="18" t="s">
         <v>58</v>
       </c>
@@ -5110,7 +5907,7 @@
       <c r="G117" s="10"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:8" x14ac:dyDescent="0.3">
       <c r="E118" s="4" t="str">
         <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E117)</f>
         <v>= LAMBDA(text,[start_delimiter],[end_delimiter],[start_instance],[end_instance],[case_sensitive],[if_not_found],
@@ -5145,7 +5942,7 @@
 )(E112, E113, F113, E114, F114, E115, E116)</v>
       </c>
     </row>
-    <row r="121" spans="2:8" s="13" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:8" s="13" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B121" s="14">
         <f xml:space="preserve"> MAX(B$1:B120) + 1</f>
         <v>2</v>
@@ -5154,27 +5951,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C123" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C127" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D128" s="31" t="s">
         <v>19</v>
       </c>
@@ -5182,7 +5979,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="129" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D129" s="31" t="s">
         <v>79</v>
       </c>
@@ -5190,19 +5987,19 @@
         <v>116</v>
       </c>
     </row>
-    <row r="130" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D130" s="31"/>
       <c r="F130" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="131" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D131" s="31"/>
       <c r="F131" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D132" s="31" t="s">
         <v>78</v>
       </c>
@@ -5210,19 +6007,19 @@
         <v>117</v>
       </c>
     </row>
-    <row r="133" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D133" s="31"/>
       <c r="F133" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="134" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D134" s="31"/>
       <c r="F134" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="135" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D135" s="31" t="s">
         <v>77</v>
       </c>
@@ -5230,13 +6027,13 @@
         <v>127</v>
       </c>
     </row>
-    <row r="136" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D136" s="31"/>
       <c r="F136" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="137" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D137" s="31"/>
       <c r="F137" s="41" t="s">
         <v>133</v>
@@ -5245,7 +6042,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D138" s="31"/>
       <c r="F138" s="41" t="s">
         <v>134</v>
@@ -5254,7 +6051,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="139" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D139" s="31" t="s">
         <v>76</v>
       </c>
@@ -5262,13 +6059,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="140" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D140" s="31"/>
       <c r="F140" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="141" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D141" s="31"/>
       <c r="F141" s="41" t="s">
         <v>133</v>
@@ -5277,7 +6074,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D142" s="31"/>
       <c r="F142" s="41" t="s">
         <v>134</v>
@@ -5286,7 +6083,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D143" s="31" t="s">
         <v>75</v>
       </c>
@@ -5294,19 +6091,19 @@
         <v>139</v>
       </c>
     </row>
-    <row r="144" spans="4:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D144" s="31"/>
       <c r="F144" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D145" s="31"/>
       <c r="F145" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D146" s="31" t="s">
         <v>32</v>
       </c>
@@ -5314,19 +6111,19 @@
         <v>124</v>
       </c>
     </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D147" s="31"/>
       <c r="F147" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D148" s="31"/>
       <c r="F148" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D149" s="31"/>
       <c r="F149" s="25" t="b">
         <v>1</v>
@@ -5335,7 +6132,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F150" s="25" t="b">
         <v>0</v>
       </c>
@@ -5343,18 +6140,18 @@
         <v>143</v>
       </c>
     </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:7" x14ac:dyDescent="0.3">
       <c r="F151" t="s">
         <v>146</v>
       </c>
       <c r="G151" s="5"/>
     </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C153" s="17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D154" s="39" t="e">
         <v>#VALUE!</v>
       </c>
@@ -5362,7 +6159,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D155" s="39" t="e">
         <v>#VALUE!</v>
       </c>
@@ -5370,7 +6167,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D156" s="39" t="e">
         <v>#VALUE!</v>
       </c>
@@ -5378,253 +6175,253 @@
         <v>151</v>
       </c>
     </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C158" s="17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D159" s="31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D160" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D161" s="32" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D162" s="32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D163" s="32" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D164" s="32" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D165" s="32" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D166" s="32" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D167" s="32" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D168" s="36" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D169" s="32" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D170" s="37" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D171" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D172" s="33" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D173" s="33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D174" s="33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D175" s="33" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D176" s="37" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D177" s="37" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D178" s="33" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D179" s="34" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D180" s="34" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D181" s="34" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D182" s="33" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D183" s="33" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D184" s="37" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D185" s="37" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D186" s="33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D187" s="34" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D188" s="35" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D189" s="35" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D190" s="35" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D191" s="34" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D192" s="34" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="193" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D193" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="194" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D194" s="33" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="195" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D195" s="37" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="196" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D196" s="33" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="197" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D197" s="34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="198" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D198" s="34" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="199" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D199" s="33" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="200" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D200" s="37" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="201" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D201" s="33" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="202" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D202" s="33" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="203" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D203" s="32" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="204" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D204" s="31" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="207" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D207" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="208" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D208" s="38" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="210" spans="2:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="2:2" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="211" spans="2:2" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B211" s="7" t="s">
         <v>3</v>
       </c>
@@ -5643,18 +6440,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2478FAD8-1E3A-4DD9-B273-ABB42BEDBDF6}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:R37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="4.28515625" customWidth="1"/>
+    <col min="1" max="3" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:18" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="2:18" s="13" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" s="13" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="14">
         <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
         <v>1</v>
@@ -5663,7 +6461,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D4" s="43" t="s">
         <v>159</v>
       </c>
@@ -5671,7 +6469,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D5" s="43" t="s">
         <v>160</v>
       </c>
@@ -5679,7 +6477,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D6" s="43" t="s">
         <v>182</v>
       </c>
@@ -5687,7 +6485,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
         <v>162</v>
       </c>
@@ -5708,12 +6506,12 @@
       <c r="Q9" s="24"/>
       <c r="R9" s="24"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C11" s="44" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D12" s="58" t="s">
         <v>168</v>
       </c>
@@ -5731,7 +6529,7 @@
       <c r="J12" s="58"/>
       <c r="K12" s="58"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D13" s="51" t="s">
         <v>171</v>
       </c>
@@ -5754,7 +6552,7 @@
         <v>= RXL_TextBetween(D13, G13, H13)</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D14" s="45" t="s">
         <v>171</v>
       </c>
@@ -5775,7 +6573,7 @@
         <v>= RXL_TextBetween(D14, G14, H14)</v>
       </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D15" s="45" t="s">
         <v>171</v>
       </c>
@@ -5796,7 +6594,7 @@
         <v>= RXL_TextBetween(D15, G15, H15)</v>
       </c>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D16" s="45" t="s">
         <v>171</v>
       </c>
@@ -5815,12 +6613,12 @@
         <v>= RXL_TextBetween(D16, G16, H16)</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C18" s="44" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D19" s="45" t="s">
         <v>174</v>
       </c>
@@ -5843,7 +6641,7 @@
         <v>= RXL_TextBetween(D19, G19, H19)</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D20" s="45" t="s">
         <v>174</v>
       </c>
@@ -5866,7 +6664,7 @@
         <v>= RXL_TextBetween(D20, G20, H20, 1, 1)</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D21" s="45" t="s">
         <v>174</v>
       </c>
@@ -5889,7 +6687,7 @@
         <v>= RXL_TextBetween(D21, G21, H21, -1, -1)</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D22" s="45" t="s">
         <v>174</v>
       </c>
@@ -5912,12 +6710,12 @@
         <v>= RXL_TextBetween(D22, G22, H22, -1, 1)</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C24" s="44" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D25" s="45" t="s">
         <v>171</v>
       </c>
@@ -5940,7 +6738,7 @@
         <v>= RXL_TextBetween(D25, G25, H25)</v>
       </c>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D26" s="45" t="s">
         <v>171</v>
       </c>
@@ -5963,7 +6761,7 @@
         <v>= RXL_TextBetween(D26, G26, H26, , , , "(not found)")</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D27" s="45" t="s">
         <v>171</v>
       </c>
@@ -5986,7 +6784,7 @@
         <v>= RXL_TextBetween(D27, G27, H27, , , , FALSE)</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D28" s="45" t="s">
         <v>171</v>
       </c>
@@ -6009,12 +6807,12 @@
         <v>= RXL_TextBetween(D28, G28, H28, , , , TRUE)</v>
       </c>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C30" s="44" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D31" s="45" t="s">
         <v>177</v>
       </c>
@@ -6037,7 +6835,7 @@
         <v>= RXL_TextBetween(D31, G31, H31, -1)</v>
       </c>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D32" s="45" t="s">
         <v>177</v>
       </c>
@@ -6060,7 +6858,7 @@
         <v>= RXL_TextBetween(D32, G32, H32, -1, , TRUE)</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D33" s="45" t="s">
         <v>177</v>
       </c>
@@ -6083,8 +6881,8 @@
         <v>= RXL_TextBetween(D33, G33, H33, -1, , FALSE)</v>
       </c>
     </row>
-    <row r="36" spans="2:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
         <v>3</v>
       </c>
@@ -6099,20 +6897,295 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B4960D-E125-4902-AE46-2BC9B841C8F4}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="B1:C110"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" s="13" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14">
+        <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B64" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" s="13" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="14">
+        <f xml:space="preserve"> MAX(B$1:B70) + 1</f>
+        <v>2</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="60" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="60"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C75" s="60" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C76" s="60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="60" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C78" s="61" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C79" s="60" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="60" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="62" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="61" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="60" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="62" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="60" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C86" s="60" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C87" s="62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C88" s="62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="60" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="62" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C91" s="60" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C92" s="60" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="60" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="60" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="60" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="60" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="60" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="60" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="62" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="60" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C102" s="62" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C103" s="62" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C104" s="60" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C105" s="62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C106" s="60" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C107" s="62" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="110" spans="2:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B110" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F99A15E-3384-4194-A934-E1FDEF2D75BB}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="B1:D10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:4" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -6120,7 +7193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>0</v>
       </c>
@@ -6131,7 +7204,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>1</v>
       </c>
@@ -6139,7 +7212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>0</v>
       </c>
@@ -6150,8 +7223,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -6163,7 +7236,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBUAEUAUwBUACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAALQAtAC0AIABUAGUAcwB0ACAAbQBvAGQAdQBsAGUAIAAtAC0ALQBcAG4AIAAgACAAIABSAFMAIAAwADgALwAwADQALwAyADAAMgA0AFwAbgAgACAAIAAgAEEAIAB0AGUAcwB0ACAARQB4AGMAZQBsACAATABhAGIAcwAgAG0AbwBkAHUAbABlACAAXABuACAAIAAgACAAQwByAGUAYQB0AGUAZAAgAGEAcwAgAGEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAGkAbgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAgACAAIAAgACAAIAAgACAAbgBhAG0AZQAgAD0AIABkAGUAZgBpAG4AaQB0AGkAbwBuADsAXABuACoALwBcAG4AXABuAC8AKgAgACAATgBBAE0ARQA6ACAAIAAgACAAIAAgACAAIABBAGIAbwB1AHQAKAApAFwAbgAgACAAIAAgAEEAVQBUAEgATwBSADoAIAAgACAAIAAgACAAUgAuAFMAaQBsAGsAXABuACAAIAAgACAAVgBFAFIAUwBJAE8ATgA6ACAAIAAgACAAIAB2ADEALgAwADAAIAAgACgAMAA4AC8AMAA0AC8AMgAwADIANAApAFwAbgAgACAAIAAgAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6ACAASABlAGwAcABlAHIAIABmAHUAbgBjAHQAaQBvAG4AIAB3AGgAaQBjAGgAIABwAHIAbwB2AGkAZABlAHMAIAB1AHMAZQByAHMAIAB3AGkAdABoACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAYQBiAG8AdQB0ACAAdABoAGUAIABmAHUAbgBjAHQAaQBvAG4AcwAgAGkAbgBjAGwAdQBkAGUAZABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgAgAEMAYQBuACAAZQBpAHQAaABlAHIAIABwAHIAbwB2AGkAZABlACAAaABpAGcAaAAtAGwAZQB2AGUAbAAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAG8AbgAgAHQAaABlACAAbQBvAGQAdQBsAGUAIABhAHMAIABhACAAdwBoAG8AbABlACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAHIAIABtAG8AcgBlACAAZABlAHQAYQBpAGwAZQBkACAAbABlAHYAZQBsACAAYQBiAG8AdQB0ACAAYQAgAHMAcABlAGMAaQBmAGkAYwAgAGYAdQBuAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgBcAG4AIAAgACAAIABQAEEAUgBBAE0ARQBUAEUAUgBTADoAIAAgAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACAAIAAgACAAWwBvAHAAdABpAG8AbgBhAGwAXQAgACAAVABoAGUAIABpAG4AZABlAHgAIABuAHUAbQBiAGUAcgAgAG8AcgAgAHMAdAByAGkAbgBnACAAbgBhAG0AZQAgAG8AZgAgAGEAIABmAHUAbgBjAHQAaQBvAG4AIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbwBtAGkAdAB0AGUAZAAgAHQAaABlACAAaABpAGcAaAAtAGwAZQB2AGUAbAAgAG0AbwBkAHUAbABlACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAaQBzACAAcgBlAHQAdQByAG4AZQBkAC4AXABuACAAIAAgACAARQBSAFIATwBSAEMASABFAEMASwBTADoAIAAoAG4AbwBuAGUAKQBcAG4AKgAvAFwAbgBBAGIAbwB1AHQAIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABbAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuAF0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAXwBuAHUAbQAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACkALAAgADAALAAgAEkARgAoACAASQBTAE4AVQBNAEIARQBSACgAcwBlAGwAZQBjAHQAXwBmAHUAbgBjAHQAaQBvAG4AKQAsACAAcwBlAGwAZQBjAHQAXwBmAHUAbgBjAHQAaQBvAG4ALAAgAC0AMQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AYQByAHIARABlAGYALAAgAEkARgAoAF8AbgB1AG0AIAA9ACAAMAAsACAAVABFAFgAVABTAFAATABJAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAYgBvAHUAdAA6AKwAVABlAHMAdAAgAG0AbwBkAHUAbABlACAAYwByAGUAYQB0AGUAZAAgAGkAbgAgAEUAeABjAGUAbAAgAEwAYQBiAHMALgB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKwAUwB1AGcAZwBlAHMAdABlAGQAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAIAA9ACAAVABFAFMAVAB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAHMAaQBvAG4AOgCsAHYAMQAuADAAMAAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHcAbgBlAHIAOgCsAFIAUwBNACAAVQBLACAARgBpAG4AYQBuAGMAaQBhAGwAIABNAG8AZABlAGwAbABpAG4AZwAgAFQAZQBhAG0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAdABoAG8AcgA6AKwAUgAgAFMAaQBsAGsAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgCsAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARgB1AG4AYwB0AGkAbwBuAKwARABlAHMAYwByAGkAcAB0AGkAbwBuAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMAAgAC0AIABBAGIAbwB1AHQArABQAHIAbwBkAHUAYwBlAHMAIAB0AGgAaQBzACAAdABhAGIAbABlACAAbwBmACAAbQBvAGQAdQBsAGUAIABpAG4AZgBvAHIAbQBhAHQAaQBvAG4AOwAgAHAAcgBvAHYAaQBkAGUAcwAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAGYAbwByACAAZQBhAGMAaAAgAGYAdQBuAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAbQBvAGQAdQBsAGUALgB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAIAAtACAAQwBFAHIAcgCsAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAIAAtACAARgBsAGEAdAB0AGUAbgCsAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAIAAtACAARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBLAGUAeQCsAFsALgAuAC4AXQBcACIALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIArABcACIALAAgAFwAIgB8AFwAIgApACwAIABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AYQByAHIATgBhAG0AZQBzACwAIABUAEUAWABUAFMAUABMAEkAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBFAHIAcgCmAFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbABhAHQAdABlAG4ApgBcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAYQB0AHQAZQBuAF8ATQB1AGwAdABpAEsAZQB5AFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgCmAFwAIgApACwAIABcAG4AIAAgACAAIAAgACAAIAAgAF8AYQByAHIASABlAGwAcAAsACAAVABFAFgAVABTAFAATABJAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQQBNAEUAOgCsAEMARQByAHIAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAEUAUwBDAFIASQBQAFQASQBPAE4AOgCsAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYARQBSAFMASQBPAE4AOgCsAHYAMQAuADAAMAAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEEAUgBBAE0ARQBUAEUAUgBTADoArAB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGUAcgByAG8AcgBfAG4AdQBtAGIAZQByAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKYAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBBAE0ARQA6AKwARgBsAGEAdAB0AGUAbgB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6AKwAWwAuAC4ALgBdAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBFAFIAUwBJAE8ATgA6AKwAdgAxAC4AMAA0ACAAIAAoADAAOAAvADAANAAvADIAMAAyADQAKQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQQBSAEEATQBFAFQARQBSAFMAOgCsAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBvAHcAXwBoAGUAYQBkAGUAcgBzAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwCsACgAcgBlAHEAdQBpAHIAZQBkACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBkAGEAdABhAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwCsACgAbwBwAHQAaQBvAG4AYQBsACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzAKwAKABvAHAAdABpAG8AbgBhAGwAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAKYAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBBAE0ARQA6AKwARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBLAGUAeQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6AKwAWwAuAC4ALgBdAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBFAFIAUwBJAE8ATgA6AKwAdgAxAC4AMAA1ACAAIAAoADAAOAAvADAANAAvADIAMAAyADQAKQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQQBSAEEATQBFAFQARQBSAFMAOgCsAHwAXAAiACAAJgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBvAHcAXwBoAGUAYQBkAGUAcgBzAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwCsACgAcgBlAHEAdQBpAHIAZQBkACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBkAGEAdABhAKwAKAByAGUAcQB1AGkAcgBlAGQAKQAgAFsALgAuAC4AXQB8AFwAIgAgACYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwCsACgAbwBwAHQAaQBvAG4AYQBsACkAIABbAC4ALgAuAF0AfABcACIAIAAmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzAKwAKABvAHAAdABpAG8AbgBhAGwAKQAgAFsALgAuAC4AXQB8AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIApgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBhAHIAcgBPAHUAdAAsACAASQBGACgAXwBuAHUAbQAgAD0AIAAtADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAF8AaQBkAHgALAAgAFMAVQBNACgAIABTAEUAUQBVAEUATgBDAEUAKAAxACwAIABDAE8AVQBOAFQAQQAoAF8AYQByAHIATgBhAG0AZQBzACkAKQAgACoAIAAoAF8AYQByAHIATgBhAG0AZQBzACAAPQAgAHMAZQBsAGUAYwB0AF8AZgB1AG4AYwB0AGkAbwBuACkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAXwBpAGQAeAAgAD4AIAAwACwAIABUAEUAWABUAFMAUABMAEkAVAAoACAASQBOAEQARQBYACgAXwBhAHIAcgBIAGUAbABwACwAIABfAGkAZAB4ACkALAAgAFwAIgCsAFwAIgAsACAAXAAiAHwAXAAiACkALAAgAFwAIgAoAEYAdQBuAGMAdABpAG8AbgAgAG4AYQBtAGUAIABuAG8AdAAgAHIAZQBjAG8AZwBuAGkAcwBlAGQAKQBcACIAKQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAXwBuAHUAbQAgAD4AIAAwACwAIABJAEYARQBSAFIATwBSACgAIABUAEUAWABUAFMAUABMAEkAVAAoACAASQBOAEQARQBYACgAXwBhAHIAcgBIAGUAbABwACwAIABfAG4AdQBtACkALAAgAFwAIgCsAFwAIgAsACAAXAAiAHwAXAAiACkALAAgAFwAIgAoAEYAdQBuAGMAdABpAG8AbgAgAGkAbgBkAGUAeAAgAG4AbwB0ACAAcgBlAGMAbwBnAG4AaQBzAGUAZAApAFwAIgApACwAIABcACIAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAXwBhAHIAcgBEAGUAZgAgAD0AIABcACIAXAAiACwAIABfAGEAcgByAE8AdQB0ACwAIABfAGEAcgByAEQAZQBmACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAqACAAIABOAEEATQBFADoAIAAgACAAIAAgACAAIAAgAEMARQByAHIAKAApAFwAbgAgACAAIAAgAEEAVQBUAEgATwBSADoAIAAgACAAIAAgACAAUgAuAFMAaQBsAGsAXABuACAAIAAgACAAVgBFAFIAUwBJAE8ATgA6ACAAIAAgACAAIAB2ADEALgAwADAAIAAgACgAMAA4AC8AMAA0AC8AMgAwADIANAApAFwAbgAgACAAIAAgAEQARQBTAEMAUgBJAFAAVABJAE8ATgA6ACAASABlAGwAcABlAHIAIABMAEEATQBCAEQAQQAgAGYAdQBuAGMAdABpAG8AbgAgAHcAaABpAGMAaAAgAGMAYQBuACAAYgBlACAAdQBzAGUAZAAgAHQAbwAgAHIAZQB0AHUAcgBuACAAYQAgAHMAcABlAGMAaQBmAGkAYwAvAGMAaABvAHMAZQBuACAARQB4AGMAZQBsACAAZQByAHIAbwByACAAYwBvAGQAZQAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQgB5ACAAcgBlAHQAdQByAG4AaQBuAGcAIABhAG4AIABFAHgAYwBlAGwAIABlAHIAcgBvAHIAIABjAG8AZABlACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAYQAgAGMAdQBzAHQAbwBtAGUAIABlAHIAcgBvAHIAIABjAG8AZABlACwAIAB0AGgAZQAgAGMAZQBsAGwAIABpAHMAIABtAGEAcgBrAGUAZAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBzACAAYQBuACAAZQByAHIAbwByACAAYgB5ACAARQB4AGMAZQBsACAAaQB0AHMAZQBsAGYALAAgAHcAaQBsAGwAIABiAGUAIABwAGkAYwBrAGUAZAAgAHUAcAAgAG8AdABoAGUAcgAgAGEAZABkAC0AaQBuAHMAIABhAG4AZAAgAHQAaABlACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdwBoAGUAbgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQB1AGQAaQB0AGkAbgBnACAAZgBvAHIAIABlAHIAcgBvAHIAcwAsACAAZQB0AGMALgBcAG4AIAAgACAAIABQAEEAUgBBAE0ARQBUAEUAUgBTADoAIAAgAGUAcgByAG8AcgBfAG4AdQBtAGIAZQByACAAIAAgAFsAcgBlAHEAdQBpAHIAZQBkAF0AIAAgAFQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIAB0AGgAZQAgAEUAeABjAGUAbAAgAGYAbwByAG0AdQBsAGEAIABlAHIAcgBvAHIAIAB5AG8AdQAgAHcAaQBzAGgAIAB0AG8AIAByAGUAdAB1AHIAbgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAbQB1AHMAdAAgAGIAZQAgAGEAbgAgAGkAbgB0AGUAZwBlAHIAIABpAG4AIAB0AGgAZQAgAHIAYQBuAGcAZQAgADAALQB0AG8ALQAxADQALgBcAG4AIAAgACAAIABFAFIAUgBPAFIAQwBIAEUAQwBLAFMAOgAgACgAbgBvAG4AZQApAFwAbgAqAC8AXABuAEMARQByAHIAIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBjAGwAYQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgAGUAcgByAG8AcgBfAG4AdQBtAGIAZQByACwAXABuACAAIAAgACAALwAvACAATQBhAGkAbgAgAHAAcgBvAGMAZQBkAHUAcgBlAFwAbgAgACAAIAAgAEwARQBUACgAZQAsACAAZQByAHIAbwByAF8AbgB1AG0AYgBlAHIALAAgAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAaQBuAHAAdQB0AHMAIAAtACAAaQBuAGkAdABpAGEAbABsAHkAIABjAGgAZQBjAGsAIABmAG8AcgAgAGEAIAB2AGEAbABpAGQAIABpAG4AcAB1AHQAIAB0AHkAcABlACAAPQA+ACAAbgB1AG0AZQByAGkAYwAgAHYAYQBsAHUAZQBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoACAATgBPAFQAKAAgAEkAUwBOAFUATQBCAEUAUgAoAGUAKQApACwAIABcACIASQBuAHYAYQBsAGkAZAAgAGUAcgByAG8AcgAgAG4AdQBtAGIAZQByACEAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAaQBuAHAAdQB0AHMAIAAtACAAaQBmACAAbgB1AG0AZQByAGkAYwAgAGkAbgBwAHUAdAAsACAAYwBoAGUAYwBrACAAaQB0ACAAaQBzACAAdwBpAHQAaABpAG4AIABlAHgAcABlAGMAdABlAGQAIAByAGEAbgBnAGUAIABhAG4AZAAgAG8AZgAgAHIAZQBxAHUAaQByAGUAZAAgAHQAeQBwAGUAIAA9AD4AIABpAG4AdABlAGcAZQByAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAAgAE8AUgAoAGUAIAA8ACAAMAAsACAAZQAgAD4AIAAxADQALAAgAE0ATwBEACgAZQAsACAAMQApACAAPAA+ACAAMAApACwAIABcACIASQBuAHYAYQBsAGkAZAAgAGUAcgByAG8AcgAgAG4AdQBtAGIAZQByACEAXAAiACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIABpAGYAIABzAHUAcABwAG8AcgB0AGUAZAAgAGUAcgByAG8AcgAgAG4AdQBtAGIAZQByAC8AdAB5AHAAZQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAAgAEkAUwBFAFIAUgBPAFIAKAAgAE0AQQBUAEMASAAoAGUALAAgAHsAMQAsADIALAAzACwANAAsADUALAA2ACwANwAsADgALAAxADMALAAxADQAfQAsADAAKQApACwAIABcACIATgBvAHQAIABzAHUAcABwAG8AcgB0AGUAZAAhAFwAIgAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHIAZQBxAHUAaQByAGUAZAAgAEUAeABjAGUAbAAgAGUAcgByAG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHAAYQBzAHMAZQBkACAAZQByAHIAbwByACAAbgB1AG0AYgBlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQAoAGUALAAgACMATgBVAEwATAAhACwAIAAjAEQASQBWAC8AMAAhACwAIAAjAFYAQQBMAFUARQAhACwAQwBhAHMAdABFAHIAcgBvAHIAIQAjAFIARQBGACEALAAgACMATgBBAE0ARQA/ACwAIAAjAE4AVQBNACEALAAgACMATgAvAEEALAAgACMARwBFAFQAVABJAE4ARwBfAEQAQQBUAEEALAAsACwALAAsACAASQBOAEQASQBSAEUAQwBUACgAXAAiAFwAIgApAC4AYQAsACAATABBAE0AQgBEAEEAKABcACIAXAAiACkAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAIAAgAE4AQQBNAEUAOgAgACAAIAAgACAAIAAgACAARgBsAGEAdAB0AGUAbgAoACkAXABuACAAIAAgACAAQQBVAFQASABPAFIAOgAgACAAIAAgACAAIABSAC4AUwBpAGwAawBcAG4AIAAgACAAIABWAEUAUgBTAEkATwBOADoAIAAgACAAIAAgAHYAMQAuADAANAAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAXABuACAAIAAgACAARABFAFMAQwBSAEkAUABUAEkATwBOADoAIABGAHUAbABsAC0AZgB1AG4AYwB0AGkAbwBuAGEAbABpAHQAeQAgAHYAZQByAHMAaQBvAG4AIABvAGYAIAB0AGgAZQAgAGYAbABhAHQALQBmAGkAbABlACAATABhAG0AYgBkAGEAIABmAHUAbgBjAHQAaQBvAG4ALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAZABlAGEAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAIABvAGYAIAB0AGgAZQAgAEcAbwBvAGcAbABlACAAUwBoAGUAZQB0AHMAIABGAEwAQQBUAFQARQBOACgAKQAgAGYAdQBuAGMAdABpAG8AbgAgAGEAbgBkACAAdABoAGUAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEAbAB0AGUAcgB5AHgAIABUAHIAYQBuAHMAcABvAHMAZQAgAHQAbwBvAGwAIAAtACAAYwBvAG4AdgBlAHIAdAAgAGEAIAAyAEQAIAB0AGEAYgBsAGUAIABpAG4AdABvACAAdgBlAHIAdABpAGMAYQBsACAAZgBsAGEAdAAtAGYAaQBsAGUAIAB3AGkAdABoACAAYQAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AIAAoAHIAbwB3ACAAdABpAHQAbABlAHMAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABuAGEAbQBlAHMAIABjAG8AbAB1AG0AbgAgACgAcgBvAHcAIABoAGUAYQBkAGUAcgBzACkALAAgAGEAbgBkACAAdgBhAGwAdQBlAHMAIABjAG8AbAB1AG0AbgAgACgAbQBhAGkAbgAgAHQAYQBiAGwAZQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwApAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAEwAYQBtAGIAZABhACAAYwByAGUAYQB0AGUAcwAgAGEAIAB0AGgAZQAgAGwAaQBzAHQAIABvAGYAIAByAG8AdwAgAGEAbgBkACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBzACAAaQBuACAAdABoAGUAIABzAHQAeQBsAGUAIABvAGYAIABhACAAQwBhAHIAdABlAHMAaQBhAG4AIABqAG8AaQBuACAAYQBuAGQAIABkAGkAcwBwAGwAYQB5AHMAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAaABpAHMAIABhAHMAIAB0AHcAbwAgAG8AcgBkAGUAcgBlAGQAIABjAG8AbAB1AG0AbgBzAC8AZgBpAGUAbABkAHMALgAgAFQAaABlACAAdgBhAGwAdQBlAHMAIABjAG8AbAB1AG0AbgAgAGEAbABvAG4AZwAgAHMAaQBkAGUAIAB0AGgAZQBzAGUAIAB1AHMAZQAgAGEAbgAgAEkATgBEAEUAWAAtAFgATQBBAFQAQwBIACgAKQAgAGEAcABwAHIAbwBhAGMAaAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABvACAAcABpAGMAawBpAG4AZwAtAHUAcAAgAHQAaABlACAAZABhAHQAYQAgAHAAbwBpAG4AdAAgAHYAYQBsAHUAZQAgAHcAaABpAGMAaAAgAGMAbwByAHIAZQBzAHAAbwBuAGQAcwAgAHQAbwAgAHQAaABlACAAYwBvAG0AYgBpAG4AYQB0AGkAbwBuACAAbwBmACAAawBlAHkAIABhAG4AZAAgAG4AYQBtAGUAIABjAG8AbAB1AG0AbgBzAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQByAGUAIABhAHIAZQAgAHQAdwBvACAAbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAgAGEAbABsAG8AdwBpAG4AZwAgAGYAbwByACAAZQBpAHQAaABlAHIAIAB0AGgAZQAgAHIAZQBwAGwAYQBjAGUAbQBlAG4AdAAgAG8AZgAgAGEAbgB5ACAAYgBsAGEAbgBrAC8AZQBtAHAAdAB5ACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAdAB1AHIAbgBlAGQAIAB3AGkAdABoACAAYQAgAHUAcwBlAHIAIABzAHAAZQBjAGkAZgBpAGUAZAAgAHYAYQBsAHUAZQAgACgAYwBhAG4AIABiAGUAIABzAHQAcgBpAG4AZwAgAG8AcgAgAG4AdQBtAGUAcgBpAGMAKQAsACAAbwByACAAYQBsAGwAbwB3ACAAZgBvAHIAIABmAGwAaQB0AGUAcgBpAG4AZwAtAG8AdQB0ACAAbwBmACAAYQBuAHkAIAByAG8AdwBzACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAYQAgAGIAbABhAG4AawAvAGUAbQBwAHQAeQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAIAB2AGEAbAB1AGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAaABpAHMAIAB2AGUAcgBzAGkAbwBuACAAbwBmACAAdABoAGUAIABMAGEAbQBiAGQAYQAgAGEAbABzAG8AIABpAG4AYwBsAHUAZABlAHMAIABjAGgAZQBjAGsAaQBuAGcAIABvAGYAIAB0AGgAZQAgAHUAcwBlAHIAIABwAGEAcwBzAGUAZAAgAHAAYQByAGEAbQBlAHQAZQByACAAdgBhAGwAdQBlAHMAIABhAG4AZAAgAHcAaQBsAGwAIABlAGkAdABoAGUAcgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHQAdQByAG4AIABhACAAcABhAHIAdABpAGMAdQBsAGEAcgAgAEUAeABjAGUAbAAgAGUAcgByAG8AcgAgAHQAeQBwAGUAIABvAHIAIAB0AGgAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABvAHUAdABwAHUAdAAgAGEAcgByAGEAeQAgAGQAZQBwAGUAbgBkAGkAbgBnACAAdQBwAG8AbgAgAHQAaABlACAAcwB0AGEAdAB1AHMAIABvAGYAIAB0AGgAZQBzAGUAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAbgBwAHUAdAAgAGMAaABlAGMAawBzAC4AXABuACAAIAAgACAAUABBAFIAQQBNAEUAVABFAFIAUwA6ACAAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIAAgACAAIABbAHIAZQBxAHUAaQByAGUAZABdACAAIABSAGEAbgBnAGUAIABvAGYAIABjAGUAbABsAHMAIABpAG4AIABhACAAcwBpAG4AZwBsAGUAIABjAG8AbAB1AG0AbgAgACgAMQArACAAcgBvAHcAcwAsACAAMQAgAGMAbwBsACkAIAB0AGgAYQB0ACAAcAByAG8AdgBpAGQAZQAgAHQAaABlACAAawBlAHkAIABmAGkAZQBsAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABbAHIAZQBxAHUAaQByAGUAZABdACAAIABSAGEAbgBnAGUAIABvAGYAIABjAGUAbABsAHMAIABpAG4AIABhACAAcwBpAG4AZwBsAGUAIAByAG8AdwAgACgAMQAgAHIAbwB3ACwAIAAxACsAIABjAG8AbAApACAAdABoAGEAdAAgAHAAcgBvAHYAaQBkAGUAIAB0AGgAZQAgAG4AYQBtAGUAIABmAGkAZQBsAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGEAdABhACAAIAAgACAAIAAgACAAIAAgACAAIABbAHIAZQBxAHUAaQByAGUAZABdACAAIABSAGEAbgBnAGUAIABvAGYAIABjAGUAbABsAHMAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABhAGIAbABlACAAcgBlAHAAcgBlAHMAZQBuAHQAaQBuAGcAIAB0AGgAZQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHQAbwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBsAGEAdAAgAGYAaQBsAGUAOwAgAGUAeABwAGUAYwB0AGUAZAAgAHQAaABhAHQAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAHcAaQBsAGwAIABtAGEAdABjAGgAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABoAGUAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgAsACAAYQBuAGQAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAHcAaQBsAGwAIABtAGEAdABjAGgAIAB0AGgAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACAAcABhAHIAYQBtAGUAdABlAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAIABbAG8AcAB0AGkAbwBuAGEAbABdACAAIABTAGkAbgBnAGwAZQAgAHYAYQBsAHUAZQAgAGkAbgBwAHUAdAAgACgAYwBhAG4AIABiAGUAIABuAHUAbQBlAHIAaQBjACwAIABzAHQAcgBpAG4AZwAgAG8AcgAgAHIAZQBmAGUAcgBlAG4AYwBlACkAOwAgAHUAcwBlAGQAIAB0AG8AIAByAGUAcABsAGEAYwBlACAAYQBuAHkAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGIAbABhAG4AawAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHcAaQB0AGgAIAB0AGgAZQAgAHUAcwBlAHIAIABwAGEAcwBzAGUAZAAgAHAAYQByAGEAbQBlAHQAZQByAC4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AbwB0AGUAOgAgAHQAaABpAHMAIAB3AGkAbABsACAAcAByAGUAdgBlAG4AdAAgAHQAaABlACAAZgBpAGwAdABlAHIAXwBiAGwAYQBuAGsAcwAgAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAIABmAHIAbwBtACAAdwBvAHIAawBpAG4AZwAgAGEAcwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZQB4AHAAZQBjAHQAZQBkACAAYQBzACAAdQBzAGUAcwAgAGIAbABhAG4AawAgAHMAdAByAGkAbgBnACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAKABcACIAXAAiACkAIABpAG4AIAB0AGgAZQAgAHYAYQBsAHUAZQBzACAAZgBpAGUAbABkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBpAGwAdABlAHIAXwBiAGwAYQBuAGsAcwAgACAAWwBvAHAAdABpAG8AbgBhAGwAXQAgACAAVABSAFUARQAvAEYAQQBMAFMARQAgAGkAbgBwAHUAdAAgAHAAYQByAGEAbQBlAHQAZQByACAAYQBsAGwAbwB3AGkAbgBnACAAdABoAGUAIAB1AHMAZQByACAAdABvACAAZgBpAGwAdABlAHIAIABvAHUAdAAgAGIAbABhAG4AawAgAHIAbwB3AHMAIAAvACAAYgBsAGEAbgBrACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABkAGEAdABhACAAcABvAGkAbgB0AHMAOwAgAHcAaQBsACAAZABlAGYAYQB1AGwAdAAgAHQAbwAgAEYAQQBMAFMARQAgAGkAZgAgAG4AbwB0ACAAcwBlAHQAIABiAHkAIAB1AHMAZQByAFwAbgAgACAAIAAgAEUAUgBSAE8AUgBDAEgARQBDAEsAUwA6ACAAIwBWAEEATABVAEUAIQAgACAAIAAgACAAIAAgACAATQBpAHMAcwBpAG4AZwAvAG8AbQBpAHQAdABlAGQAIABuAG8AbgAtAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIAAoAHIAbwB3AF8AaABlAGEAZABlAHIAcwAsACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACwAIABkAGEAdABhACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAGgAYQB2AGUAIABhAHQAIABsAGUAYQBzAHQAIAAxACAAcgBvAHcALAAgAG8AcgAgAGgAYQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIAAxACAAYwBvAGwAdQBtAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAGgAYQB2AGUAIABhAHQAIABsAGUAYQBzAHQAIAAxACAAYwBvAGwAdQBtAG4ALAAgAG8AcgAgAGgAYQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIAAxACAAcgBvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIABkAGEAdABhACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABoAGEAdgBlACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAHIAbwB3ACAAYQBuAGQAIABhAHQAIABsAGUAYQBzAHQAIAAxACAAYwBvAGwAdQBtAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAEMAQQBMAEMAIQAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAcgBvAHcAcwAgAGkAbgAgAHQAaABlACAAcABhAHMAcwBlAGQAIABkAGEAdABhACAAdABhAGIAbABlACAAKABkAGEAdABhACkAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAbwB3AHMAIABpAG4AIAB0AGgAZQAgAHIAbwB3AF8AaABlAGEAZABlAHIAcwAgAHAAYQByAGEAbQBlAHQAZQByADsAIABvAHIAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAGkAbgAgAHQAaABlACAAcABhAHMAcwBlAGQAIABkAGEAdABhACAAdABhAGIAbABlACAAKABkAGEAdABhACkAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAbwBlAHMAIABuAG8AdAAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABpAG4AIAB0AGgAZQAgAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwAgAHAAYQByAGEAbQBlAHQAZQByAFwAbgAqAC8AXABuAEYAbABhAHQAdABlAG4AIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBjAGwAYQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgAHIAbwB3AF8AaABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAcwAsAFwAbgAgACAAIAAgAGQAYQB0AGEALABcAG4AIAAgACAAIABbAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwBdACwAXABuACAAIAAgACAAWwBmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzAF0ALABcAG4AIAAgACAAIAAvAC8AIABNAGEAaQBuACAAcAByAG8AYwBlAGQAdQByAGUAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAF8AcgBoACwAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgAF8AYwBoACwAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZABkACwAIABkAGEAdABhACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgACAALQAtAD4AIABpAHMAcwB1AGUAcwAgAGkAbgAgAHQAaABlACAAbQBhAGkAbgAgAHAAYQBzAHMAZQBkACAAcABhAHIAYQBtAGUAdABlAHIAcwAgAHcAaQBsAGwAIABnAGkAdgBlACAAYQAgACMAVgBBAEwAVQBFACEAIABlAHIAcgBvAHIAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAbQBpAHMAbQBhAHQAYwBoACAAaQBuACAAYQByAHIAYQB5ACAAcwBpAHoAZQAgAG8AZgAgAGQAYQB0AGEAIAB0AGEAYgBsAGUAIABhAG4AZAAgAHIAbwB3AF8AaABlAGEAZABlAHIAIABhAG4AZAAgAGMAbwBsAHUAbQBuAF8AaABlAGEAZABlAHIAIAByAGEAbgBnAGUAcwAgAHcAaQBsAGwAIABnAGkAdgBlACAAYQAgACMAQwBBAEwAQwAhACAAZQByAHIAbwByAFwAbgAgACAAIAAgACAAIAAgACAAXwBpAG4AcABDAGgAawAsACAASQBGAFMAKAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAIABPAFIAKAAgAFIATwBXAFMAKABfAHIAaAApACAAPAAgADEALAAgAEMATwBMAFUATQBOAFMAKABfAHIAaAApACAAPAA+ACAAMQAsACAAUgBPAFcAUwAoAF8AYwBoACkAIAA8AD4AIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBjAGgAKQAgADwAIAAxACwAIABSAE8AVwBTACgAXwBkAGQAKQAgADwAIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBkAGQAKQAgADwAIAAxACkALAAgADMAKQAsACAAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAIABPAFIAKAAgAFIATwBXAFMAKABfAGQAZAApACAAPAA+ACAAUgBPAFcAUwAoAF8AcgBoACkALAAgAEMATwBMAFUATQBOAFMAKABfAGQAZAApACAAPAA+ACAAQwBPAEwAVQBNAE4AUwAoAF8AYwBoACkAKQAsACAAMwApACwAIAAxADQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABEAGUAYQBsACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABhAG4AZAAgAHMAZQB0ACAAZABlAGYAYQB1AGwAdAAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAXwByAHAALAAgAEkARgAoACAASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAKQAsACAAXAAiAFwAIgAsACAAcgBlAHAAbABhAGMAZQBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBsAHQAcgAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAHQAZQByAF8AYgBsAGEAbgBrAHMAKQAsACAARgBBAEwAUwBFACwAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIABrAGUAeQAgAGYAaQBlAGwAZAAgAC0ALQAgAHIAZQBwAGUAYQB0AHMAIAB0AGgAZQAgAGMAbwBsAHUAbQBuACAAbwBmACAAcgBvAHcAIAB0AGkAdABsAGUAcwAgAHQAbwAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgAgAGgAZQBhAGQAZQByAHMAIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAcwAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAXwBrAGUAeQAsACAAVABPAEMATwBMACgAIABJAEYAKAAgAFMARQBRAFUARQBOAEMARQAoADEALAAgAEMATwBMAFUATQBOAFMAKABfAGMAaAApACkALAAgAF8AcgBoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwByAGUAYQB0AGUAIAB0AGgAZQAgAG4AYQBtAGUAcwAgAGYAaQBlAGwAZAAgAC0ALQAgAHIAZQBwAGUAYQB0AHMAIAB0AGgAZQAgAHIAbwB3ACAAbwBmACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBzACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3ACAAdABpAHQAbABlAHMAIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAcwAgAHQAbwAgAGEAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAXwBuAGEAbQBlAHMALAAgAFQATwBDAE8ATAAoACAASQBGACgAIABTAEUAUQBVAEUATgBDAEUAKAAgAFIATwBXAFMAKABfAHIAaAApACwAIAAxACkALAAgAF8AYwBoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwByAGUAYQB0AGUAIAB0AGgAZQAgAHYAYQBsAHUAZQBzACAAZgBpAGUAbABkACAALQAtACAAdQBzAGUAcwAgAGEAbgAgAEkATgBEAEUAWAAtAFgATQBBAFQAQwBIACAAbQBlAHQAaABvAGQAbwBsAG8AZwB5ACAAdABvACAAZwBlAHQAIAB0AGgAZQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAGsAZQB5ACAAYQBuAGQAIABuAGEAbQBlAHMAIABmAGkAZQBsAGQAcwA7ACAAZQBtAHAAdAB5ACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAdwBpAGwAbAAgAHMAaABvAHcAIABhAHMAIAAwACAAKAB6AGUAcgBvACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAdABlAHMAdABzACAAZgBvAHIAIABiAGwAYQBuAGsAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIABhAG4AZAAgAHIAZQBwAGwAYQBjAGUAcwAgAHcAaQB0AGgAIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwAgAHAAYQByAGEAbQBlAHQAZQByAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgAGIAeQAgAGQAZQBmAGEAdQBsAHQAIABiAGwAYQBuAGsAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIABhAHIAZQAgAHAAcgBlAHMAZQByAHYAZQBkACAAdQBzAGkAbgBnACAAYQAgAE4AdQBsAGwAUwB0AHIAaQBuAGcAIAAoAFwAIgBcACIAKQAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAbwBwAHQAaQBvAG4AYQBsACAAZgBpAGwAdABlAHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABfAHYAYQBsAHUAZQBzACwAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGQAcAAsACAASQBOAEQARQBYACgAXwBkAGQALAAgAFgATQBBAFQAQwBIACgAXwBrAGUAeQAsACAAXwByAGgALAAgADAAKQAsACAAWABNAEEAVABDAEgAKABfAG4AYQBtAGUAcwAsACAAXwBjAGgALAAgADAAKQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAIABJAFMAQgBMAEEATgBLACgAXwBkAHAAKQAsACAAXwByAHAALAAgAF8AZABwACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAG8AdQB0AHAAdQB0ACAALQAtACAAcwB0AGEAYwBrACAAawBlAHkALAAgAG4AYQBtAGUAIABhAG4AZAAgAHYAYQBsAHUAZQAgAGMAbwBsAHUAbQBuAHMAIAAoAF8AZAB0ACkALAAgAGEAbgBkACAAZgBpAGwAdABlAHIAIABiAGwAYQBuAGsAcwAgAHYAYQBsAHUAZQAgAHIAbwB3AHMAIABpAGYAIAByAGUAcQB1AGkAcgBlAGQAIAAoAF8AZgBsAHQAcgApAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgACAAdABoAGUAIAByAG8AdwAgAGYAaQBsAHQAZQByAGkAbgBnACAAcgBlAGwAaQBlAHMAIABvAG4AIABiAGwAYQBuAGsAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIAB1AHMAaQBuAGcAIABOAHUAbABsAFMAdAByAGkAbgBnACAAKABcACIAXAAiACkAIAB0AG8AIAB3AG8AcgBrACAAYwBvAHIAcgBlAGMAdABsAHkALAAgAHMAbwAgAHcAaQBsAGwAIABuAG8AdAAgAGYAdQBuAGMAdABpAG8AbgAgAGkAZgAgAHQAaABlACAAcgBlAHAAbABhAGMAZQBfAGIAbABhAG4AawBzACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzACAAdQBzAGUAZABcAG4AIAAgACAAIAAgACAAIAAgAF8AYwBhAGwAYwAsACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBkAHQALAAgAEgAUwBUAEEAQwBLACgAXwBrAGUAeQAsACAAXwBuAGEAbQBlAHMALAAgAF8AdgBhAGwAdQBlAHMAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAF8AZgBsAHQAcgAsACAARgBJAEwAVABFAFIAKABfAGQAdAAsACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAF8AZAB0ACwAIAAtADEAKQAgADwAPgAgAFwAIgBcACIAKQAsACAAXwBkAHQAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBlAHQAdQByAG4AIAB2AGEAbAB1AGUAIABkAGUAcABlAG4AZABpAG4AZwAgAG8AbgAgAGkAbgBwAHUAdAAgAGMAaABlAGMAawBzACAAcwB0AGEAdAB1AHMAIAAtAC0AIABmAG8AcgAgAGkAbgBwAHUAdAAgAGMAaABlAGMAawAgAGYAYQBpAGwAdQByAGUAIAByAGUAdAB1AHIAbgAgAGEAIAAjAFYAQQBMAFUARQAhACAAZQByAHIAbwByACwAIABvAHQAaABlAHIAdwBpAHMAZQAgAHIAZQB0AHUAcgBuACAAdABoAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAcgBlAHMAdQBsAHQAIAAoAF8AYwBhAGwAYwApAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAXwBpAG4AcABDAGgAawAgAD0AIAAwACwAIABfAGMAYQBsAGMALAAgAFIAUwBfAEMARQByAHIAKABfAGkAbgBwAEMAaABrACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgAvACoAIAAgAE4AQQBNAEUAOgAgACAAIAAgACAAIAAgACAARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBLAGUAeQAoACkAXABuACAAIAAgACAAQQBVAFQASABPAFIAOgAgACAAIAAgACAAIABSAC4AUwBpAGwAawBcAG4AIAAgACAAIABWAEUAUgBTAEkATwBOADoAIAAgACAAIAAgAHYAMQAuADAANQAgACAAKAAwADgALwAwADQALwAyADAAMgA0ACkAXABuACAAIAAgACAARABFAFMAQwBSAEkAUABUAEkATwBOADoAIABBAG4AIABlAHgAdABlAG4AcwBpAG8AbgAgAG8AZgAgAHQAaABlACAAZgB1AGwAbAAtAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAIABSAFMAXwBGAGwAYQB0AHQAZQBuACgAKQAgAGYAdQBuAGMAdABpAG8AbgAuACAAVABoAGkAcwAgAEwAYQBtAGIAZABhACAAYQBsAGwAbwB3AHMAIABmAG8AcgAgAG0AdQBsAHQAaQBwAGwAZQAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAYQBzACAAbABvAG4AZwAgAGEAcwAgAHQAaABlAHkAIABhAHIAZQAgAGkAbgAgAGEAIABjAG8AbgB0AGkAZwB1AG8AdQBzACAAcgBhAG4AZwBlACkAIABpAG4AIABhACAAcwBpAG0AaQBsAGEAcgAgAG0AYQBuAG4AZQByACAAdABvACAAdABoAGUAIABBAGwAdABlAHIAeQB4ACAAVAByAGEAbgBzAHAAbwBzAGUAIAB0AG8AbwBsAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAGMAcgBlAGEAdABlAGQAIABrAGUAeQAgAGYAaQBlAGwAZAAgAGkAcwAgAGMAaABhAG4AZwBlAGQAIAB0AG8AIABfAGsAZQB5AHMAIABhAG4AZAAgAHUAcwBlAHMAIABhACAAZABpAGYAZgBlAHIAZQBuAHQAIABhAHAAcAByAG8AYQBjAGgAIAB0AG8AIABpAHQAcwAgAGMAbwBuAHMAdAB1AGMAdABpAG8AbgAgAHcAaQB0AGgAIAB0AGgAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAApACAAZgB1AG4AYwB0AGkAbwBuAC4AIABUAGgAZQAgAGUAYQByAGwAaQBlAHIAIAB2AGUAcgBzAGkAbwBuAHMAIABvAGYAIAB0AGgAZQAgAGYAbABhAHQALQBmAGkAbABlACAATABhAG0AYgBkAGEAIABjAHIAZQBhAHQAZQAgAHQAaABlACAAawBlAHkAIABmAGkAZQBsAGQAIABhAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAbQBhAGQAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdQBwACAAbwBmACAAdABoAGUAIABzAGkAbgBnAGwAZQAgAGMAbwBsAHUAbQBuACAAbwBmACAAcgBvAHcAIAB0AGkAdABsAGUAcwAgAHIAZQBwAGUAYQB0AGUAZAAgAGEAYwByAG8AcwBzACAAdABoAGUAIABzAGEAbQBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAYQBzACAAdABoAGUAcgBlACAAYQByAGUAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB0AGgAZQAgAHMAZQBsAGUAYwB0AGUAZAAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAcwAgAC0AIAB0AGgAaQBzACAAMgBEACAAYQByAHIAYQB5ACAAaQBzACAAdABoAGUAbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAYQAgAHMAaQBuAGcAbABlACAAYwBvAGwAdQBtAG4AIAB1AHMAaQBuAGcAIAB0AGgAZQAgAFQATwBDAE8ATAAoACkAIABmAHUAbgBjAHQAaQBvAG4AIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHMAYwBhAG4AbgBpAG4AZwAgAGEAYwByAG8AcwBzACAAcgBvAHcAcwAuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABlAHgAdABlAG4AZABlAGQAIABtAGUAdABoAG8AZABvAGwAbwBnAHkAIABjAG8AbgBzAHQAcgB1AGMAdABzACAAdABoAGUAIABrAGUAeQBzACAAZgBpAGUAbABkACAAdQBzAGkAbgBnACAAdABoAGUAIABNAEEASwBFAEEAUgBSAEEAWQAoACkAIABmAHUAbgBjAHQAaQBvAG4AIAB3AGgAZQByAGUAIABhACAAMgBEACAAYQByAHIAYQB5ACAAaQBzACAAYwByAGUAYQB0AGUAZAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAdwBoAGkAYwBoACAAaQBzACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3ACAAdABpAHQAbABlACAAcgBvAHcAcwAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAB0AGgAeQBlACAAbgB1AG0AYgBlAHIAIABvAGYAIABjAG8AbAB1AG0AbgAgAGgAZQBhAGQAZQByACAAYwBvAGwAdQBtAG4AcwAgAHQAYQBsAGwAIABiAHkAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIABzAGUAbABlAGMAdABlAGQAIAByAG8AdwAgAHQAaQB0AGwAZQBzACAAcgBhAG4AZwBlAC4AIABUAGgAaQBzACAAMgBEACAAYQByAHIAYQB5ACAAaQBzACAAdABoAGUAbgAgAHAAbwBwAHUAbABhAHQAZQBkACAAYgB5ACAAdABoAGUAIABNAEEASwBFAEEAUgBSAEEAWQAoACkAIABMAGEAbQBiAGQAYQAgAHUAcwBpAG4AZwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYQBuACAASQBOAEQARQBYACgAKQAgAGYAdQBuAGMAdABpAG8AbgAgAG8AbgAgAHQAaABlACAAbwByAGkAZwBpAG4AYQBsAGwAeQAgAHMAZQBsAGUAYwB0AGUAZAAgAHIAbwB3ACAAdABpAHQAbABlAHMAIAByAGEAbgBnAGUALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMAdQByAHIAZQBuAHQAbAB5ACAAYQAgAHMAaQBtAHAAbABlACAAbQBlAHQAaABvAGQAbwBsAG8AZwB5ACAAKABUAE8AQwBPAEwAKAApACkAIABpAHMAIAB1AHMAZQBkACAAdABvACAAcABvAHAAdQBsAGEAdABlACAAdABoAGUAIAB2AGEAbAB1AGUAcwAgAGYAaQBlAGwAZAAsACAAdwBoAGkAYwBoACAAdwBvAHUAbABkACAAaQBkAGUAYQBsAGwAeQAgAGIAZQAgAHUAcABkAGEAdABlAGQAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHQAbwAgAGEAIABtAG8AcgBlACAAcgBvAGIAdQBzAHQAIABtAGUAdABoAG8AZABvAGwAbwBnAHkAIABzAHUAYwBoACAAYQBzACAAdABoAGUAIABJAE4ARABFAFgALQBYAE0AQQBUAEMASAAgAGEAcABwAHIAbwBhAGMAaAAuAFwAbgAgACAAIAAgAFAAQQBSAEEATQBFAFQARQBSAFMAOgAgACAAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACAAIAAgACAAWwByAGUAcQB1AGkAcgBlAGQAXQAgACAAUgBhAG4AZwBlACAAbwBmACAAYwBlAGwAbABzACAAaQBuACAAYQAgAHMAaQBuAGcAbABlACAAYwBvAGwAdQBtAG4AIAAoADEAKwAgAHIAbwB3AHMALAAgADEAIABjAG8AbAApACAAdABoAGEAdAAgAHAAcgBvAHYAaQBkAGUAIAB0AGgAZQAgAGsAZQB5ACAAZgBpAGUAbABkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACAAWwByAGUAcQB1AGkAcgBlAGQAXQAgACAAUgBhAG4AZwBlACAAbwBmACAAYwBlAGwAbABzACAAaQBuACAAYQAgAHMAaQBuAGcAbABlACAAcgBvAHcAIAAoADEAIAByAG8AdwAsACAAMQArACAAYwBvAGwAKQAgAHQAaABhAHQAIABwAHIAbwB2AGkAZABlACAAdABoAGUAIABuAGEAbQBlACAAZgBpAGUAbABkAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZABhAHQAYQAgACAAIAAgACAAIAAgACAAIAAgACAAWwByAGUAcQB1AGkAcgBlAGQAXQAgACAAUgBhAG4AZwBlACAAbwBmACAAYwBlAGwAbABzACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAYQBiAGwAZQAgAHIAZQBwAHIAZQBzAGUAbgB0AGkAbgBnACAAdABoAGUAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIAB0AG8AIABmAGwAYQB0ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbABlADsAIABlAHgAcABlAGMAdABlAGQAIAB0AGgAYQB0ACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIAB3AGkAbABsACAAbQBhAHQAYwBoACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIABpAG4AIAB0AGgAZQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACAAcABhAHIAYQBtAGUAdABlAHIALAAgAGEAbgBkACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIAB3AGkAbABsACAAbQBhAHQAYwBoACAAdABoAGUAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBwAGwAYQBjAGUAXwBiAGwAYQBuAGsAcwAgAFsAbwBwAHQAaQBvAG4AYQBsAF0AIAAgAFMAaQBuAGcAbABlACAAdgBhAGwAdQBlACAAaQBuAHAAdQB0ACAAKABjAGEAbgAgAGIAZQAgAG4AdQBtAGUAcgBpAGMALAAgAHMAdAByAGkAbgBnACAAbwByACAAcgBlAGYAZQByAGUAbgBjAGUAKQA7ACAAdQBzAGUAZAAgAHQAbwAgAHIAZQBwAGwAYQBjAGUAIABhAG4AeQAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAYgBsAGEAbgBrACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAdwBpAHQAaAAgAHQAaABlACAAdQBzAGUAcgAgAHAAYQBzAHMAZQBkACAAcABhAHIAYQBtAGUAdABlAHIALgAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBvAHQAZQA6ACAAdABoAGkAcwAgAHcAaQBsAGwAIABwAHIAZQB2AGUAbgB0ACAAdABoAGUAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACAAZgB1AG4AYwB0AGkAbwBuAGEAbABpAHQAeQAgAGYAcgBvAG0AIAB3AG8AcgBrAGkAbgBnACAAYQBzACAAZQB4AHAAZQBjAHQAZQBkACAAYQBzACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAB1AHMAZQBzACAAYgBsAGEAbgBrACAAcwB0AHIAaQBuAGcAIABkAGEAdABhACAAcABvAGkAbgB0AHMAIAAoAFwAIgBcACIAKQAgAGkAbgAgAHQAaABlACAAdgBhAGwAdQBlAHMAIABmAGkAZQBsAGQAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACAAIABbAG8AcAB0AGkAbwBuAGEAbABdACAAIABUAFIAVQBFAC8ARgBBAEwAUwBFACAAaQBuAHAAdQB0ACAAcABhAHIAYQBtAGUAdABlAHIAIABhAGwAbABvAHcAaQBuAGcAIAB0AGgAZQAgAHUAcwBlAHIAIAB0AG8AIABmAGkAbAB0AGUAcgAgAG8AdQB0ACAAYgBsAGEAbgBrACAAcgBvAHcAcwAgAC8AIABiAGwAYQBuAGsAIABkAGEAdABhACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAG8AaQBuAHQAcwA7ACAAdwBpAGwAIABkAGUAZgBhAHUAbAB0ACAAdABvACAARgBBAEwAUwBFACAAaQBmACAAbgBvAHQAIABzAGUAdAAgAGIAeQAgAHUAcwBlAHIAXABuACAAIAAgACAARQBSAFIATwBSAEMASABFAEMASwBTADoAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIABNAGkAcwBzAGkAbgBnAC8AbwBtAGkAdAB0AGUAZAAgAG4AbwBuAC0AbwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAgACgAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACwAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMALAAgAGQAYQB0AGEAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACMAVgBBAEwAVQBFACEAIAAgACAAIAAgACAAIAAgAHIAbwB3AF8AaABlAGEAZABlAHIAcwAgAHAAYQByAGEAbQBlAHQAZQByACAAZABvAGUAcwAgAG4AbwB0ACAAaABhAHYAZQAgAGEAdAAgAGwAZQBhAHMAdAAgADEAIAByAG8AdwAgAGEAbgBkACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIwBWAEEATABVAEUAIQAgACAAIAAgACAAIAAgACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABoAGEAdgBlACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAGMAbwBsAHUAbQBuACwAIABvAHIAIABoAGEAcwAgAG0AbwByAGUAIAB0AGgAYQBuACAAMQAgAHIAbwB3AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIwBWAEEATABVAEUAIQAgACAAIAAgACAAIAAgACAAZABhAHQAYQAgAHAAYQByAGEAbQBlAHQAZQByACAAZABvAGUAcwAgAG4AbwB0ACAAaABhAHYAZQAgAGEAdAAgAGwAZQBhAHMAdAAgADEAIAByAG8AdwAgAGEAbgBkACAAYQB0ACAAbABlAGEAcwB0ACAAMQAgAGMAbwBsAHUAbQBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIwBDAEEATABDACEAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAHIAbwB3AHMAIABpAG4AIAB0AGgAZQAgAHAAYQBzAHMAZQBkACAAZABhAHQAYQAgAHQAYQBiAGwAZQAgACgAZABhAHQAYQApACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAbwBmACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAG8AdwBzACAAaQBuACAAdABoAGUAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgA7ACAAbwByAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMAIABpAG4AIAB0AGgAZQAgAHAAYQBzAHMAZQBkACAAZABhAHQAYQAgAHQAYQBiAGwAZQAgACgAZABhAHQAYQApACAAcABhAHIAYQBtAGUAdABlAHIAIABkAG8AZQBzACAAbgBvAHQAIABtAGEAdABjAGgAIAB0AGgAZQAgAG4AdQBtAGIAZQByACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABvAGYAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAdABoAGUAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMAIABwAGEAcgBhAG0AZQB0AGUAcgBcAG4AKgAvAFwAbgBGAGwAYQB0AHQAZQBuAF8ATQB1AGwAdABpAGsAZQB5ACAAPQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAALwAvACAAUABhAHIAYQBtAGUAdABlAHIAIABkAGUAYwBsAGEAcgBhAHQAaQBvAG4AcwBcAG4AIAAgACAAIAByAG8AdwBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByAHMALABcAG4AIAAgACAAIABkAGEAdABhACwAXABuACAAIAAgACAAWwByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAXQAsAFwAbgAgACAAIAAgAFsAZgBpAGwAdABlAHIAXwBiAGwAYQBuAGsAcwBdACwAXABuACAAIAAgACAALwAvACAATQBhAGkAbgAgAHAAcgBvAGMAZQBkAHUAcgBlAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABfAHIAaAAsACAAcgBvAHcAXwBoAGUAYQBkAGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIABfAGMAaAAsACAAYwBvAGwAdQBtAG4AXwBoAGUAYQBkAGUAcgBzACwAXABuACAAIAAgACAAIAAgACAAIABfAGQAZAAsACAAZABhAHQAYQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQwBoAGUAYwBrACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAaQBzAHMAdQBlAHMAIABpAG4AIAB0AGgAZQAgAG0AYQBpAG4AIABwAGEAcwBzAGUAZAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIAB3AGkAbABsACAAZwBpAHYAZQAgAGEAIAAjAFYAQQBMAFUARQAhACAAZQByAHIAbwByAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgAG0AaQBzAG0AYQB0AGMAaAAgAGkAbgAgAGEAcgByAGEAeQAgAHMAaQB6AGUAIABvAGYAIABkAGEAdABhACAAdABhAGIAbABlACAAYQBuAGQAIAByAG8AdwBfAGgAZQBhAGQAZQByACAAYQBuAGQAIABjAG8AbAB1AG0AbgBfAGgAZQBhAGQAZQByACAAcgBhAG4AZwBlAHMAIAB3AGkAbABsACAAZwBpAHYAZQAgAGEAIAAjAEMAQQBMAEMAIQAgAGUAcgByAG8AcgBcAG4AIAAgACAAIAAgACAAIAAgAF8AaQBuAHAAQwBoAGsALAAgAEkARgBTACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAgAE8AUgAoACAAUgBPAFcAUwAoAF8AcgBoACkAIAA8ACAAMQAsACAAQwBPAEwAVQBNAE4AUwAoAF8AcgBoACkAIAA8ACAAMQAsACAAUgBPAFcAUwAoAF8AYwBoACkAIAA8AD4AIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBjAGgAKQAgADwAIAAxACwAIABSAE8AVwBTACgAXwBkAGQAKQAgADwAIAAxACwAIABDAE8ATABVAE0ATgBTACgAXwBkAGQAKQAgADwAIAAxACkALAAgADMAKQAsACAAMwAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAIABPAFIAKAAgAFIATwBXAFMAKABfAGQAZAApACAAPAA+ACAAUgBPAFcAUwAoAF8AcgBoACkALAAgAEMATwBMAFUATQBOAFMAKABfAGQAZAApACAAPAA+ACAAQwBPAEwAVQBNAE4AUwAoAF8AYwBoACkAKQAsACAAMwApACwAIAAxADQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABEAGUAYQBsACAAdwBpAHQAaAAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAIABhAG4AZAAgAHMAZQB0ACAAZABlAGYAYQB1AGwAdAAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAXwByAHAALAAgAEkARgAoACAASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAKQAsACAAXAAiAFwAIgAsACAAcgBlAHAAbABhAGMAZQBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBsAHQAcgAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAGYAaQBsAHQAZQByAF8AYgBsAGEAbgBrAHMAKQAsACAARgBBAEwAUwBFACwAIABmAGkAbAB0AGUAcgBfAGIAbABhAG4AawBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIABrAGUAeQAgAGYAaQBlAGwAZABzACAALQAtACAAdQBzAGUAcwAgAHQAaABlACAATQBBAEsARQBBAFIAUgBBAFkAKAApACAAZgB1AG4AYwB0AGkAbwBuACAAdABvACAAYwByAGUAYQB0AGUAIAByAGUAcABlAGEAdAAgAGIAbABvAGMAawBzACAAbwBmACAAdABoAGUAIABzAGUAbABlAGMAdABlAGQAIAByAG8AdwBfAGgAZQBhAGQAZQByACAALwAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AKABzACkAIABhAGwAbABvAHcAaQBuAGcAIABmAG8AcgAgADEAKwAgAGsAZQB5ACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAF8AawBlAHkAcwAsACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwByAHIALAAgAFIATwBXAFMAKABfAHIAaAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AcgBjACwAIABDAE8ATABVAE0ATgBTACgAXwByAGgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGMAYwAsACAAQwBPAEwAVQBNAE4AUwAoAF8AYwBoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKABfAHIAcgAgACoAIABfAGMAYwAsACAAXwByAGMALAAgAEwAQQBNAEIARABBACgAXwByAG8AdwAsAF8AYwBvAGwALAAgAEkATgBEAEUAWAAoAF8AcgBoACwAIABGAEwATwBPAFIALgBNAEEAVABIACgAKABfAHIAbwB3ACAALQAgADEAKQAgAC8AIABfAGMAYwApACAAKwAgADEAKQApACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIABuAGEAbQBlAHMAIABmAGkAZQBsAGQAIAAtAC0AIAByAGUAcABlAGEAdABzACAAdABoAGUAIAByAG8AdwAgAG8AZgAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAcwAgAHQAbwAgAG0AYQB0AGMAaAAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwAgAHQAaQB0AGwAZQBzACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AHMAIAB0AG8AIABhACAAcwBpAG4AZwBsAGUAIABjAG8AbAB1AG0AbgBcAG4AIAAgACAAIAAgACAAIAAgAF8AbgBhAG0AZQBzACwAIABUAE8AQwBPAEwAKAAgAEkARgAoACAAUwBFAFEAVQBFAE4AQwBFACgAIABSAE8AVwBTACgAXwByAGgAKQAsACAAMQApACwAIABfAGMAaAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAcgBlAGEAdABlACAAdABoAGUAIAB2AGEAbAB1AGUAcwAgAGYAaQBlAGwAZAAgAC0ALQAgAHUAcwBlAHMAIABhAG4AIABJAE4ARABFAFgALQBYAE0AQQBUAEMASAAgAG0AZQB0AGgAbwBkAG8AbABvAGcAeQAgAHQAbwAgAGcAZQB0ACAAdABoAGUAIABkAGEAdABhACAAcABvAGkAbgB0ACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIABrAGUAeQAgAGEAbgBkACAAbgBhAG0AZQBzACAAZgBpAGUAbABkAHMAOwAgAGUAbQBwAHQAeQAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHcAaQBsAGwAIABzAGgAbwB3ACAAYQBzACAAMAAgACgAegBlAHIAbwApAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgAHQAZQBzAHQAcwAgAGYAbwByACAAYgBsAGEAbgBrACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAYQBuAGQAIAByAGUAcABsAGEAYwBlAHMAIAB3AGkAdABoACAAdABoAGUAIABvAHAAdABpAG8AbgBhAGwAIAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAIABwAGEAcgBhAG0AZQB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgACAALQAtAD4AIABiAHkAIABkAGUAZgBhAHUAbAB0ACAAYgBsAGEAbgBrACAAZABhAHQAYQAgAHAAbwBpAG4AdABzACAAYQByAGUAIABwAHIAZQBzAGUAcgB2AGUAZAAgAHUAcwBpAG4AZwAgAGEAIABOAHUAbABsAFMAdAByAGkAbgBnACAAKABcACIAXAAiACkAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAG8AcAB0AGkAbwBuAGEAbAAgAGYAaQBsAHQAZQByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAXwB2AGEAbAB1AGUAcwAsACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBkAHAALAAgAFQATwBDAE8ATAAoAF8AZABkACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAIABJAFMAQgBMAEEATgBLACgAXwBkAHAAKQAsACAAXwByAHAALAAgAF8AZABwACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAbwB1AHQAcAB1AHQAIAAtAC0AIABzAHQAYQBjAGsAIABrAGUAeQAsACAAbgBhAG0AZQAgAGEAbgBkACAAdgBhAGwAdQBlACAAYwBvAGwAdQBtAG4AcwAgACgAXwBkAHQAKQAsACAAYQBuAGQAIABmAGkAbAB0AGUAcgAgAGIAbABhAG4AawBzACAAdgBhAGwAdQBlACAAcgBvAHcAcwAgAGkAZgAgAHIAZQBxAHUAaQByAGUAZAAgACgAXwBmAGwAdAByACkAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIAAgAC0ALQA+ACAAIAB0AGgAZQAgAHIAbwB3ACAAZgBpAGwAdABlAHIAaQBuAGcAIAByAGUAbABpAGUAcwAgAG8AbgAgAGIAbABhAG4AawAgAGQAYQB0AGEAIABwAG8AaQBuAHQAcwAgAHUAcwBpAG4AZwAgAE4AdQBsAGwAUwB0AHIAaQBuAGcAIAAoAFwAIgBcACIAKQAgAHQAbwAgAHcAbwByAGsAIABjAG8AcgByAGUAYwB0AGwAeQAsACAAcwBvACAAdwBpAGwAbAAgAG4AbwB0ACAAZgB1AG4AYwB0AGkAbwBuACAAaQBmACAAdABoAGUAIAByAGUAcABsAGEAYwBlAF8AYgBsAGEAbgBrAHMAIABmAHUAbgBjAHQAaQBvAG4AIABpAHMAIAB1AHMAZQBkAFwAbgAgACAAIAAgACAAIAAgACAAXwBjAGEAbABjACwAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGQAdAAsACAASABTAFQAQQBDAEsAKABfAGsAZQB5AHMALAAgAF8AbgBhAG0AZQBzACwAIABfAHYAYQBsAHUAZQBzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAXwBmAGwAdAByACwAIABGAEkATABUAEUAUgAoAF8AZAB0ACwAIABDAEgATwBPAFMARQBDAE8ATABTACgAXwBkAHQALAAgAC0AMQApACAAPAA+ACAAXAAiAFwAIgApACwAIABfAGQAdAApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABTAGUAbABlAGMAdAAgAHIAZQB0AHUAcgBuACAAdgBhAGwAdQBlACAAZABlAHAAZQBuAGQAaQBuAGcAIABvAG4AIABpAG4AcAB1AHQAIABjAGgAZQBjAGsAcwAgAHMAdABhAHQAdQBzACAALQAtACAAZgBvAHIAIABpAG4AcAB1AHQAIABjAGgAZQBjAGsAIABmAGEAaQBsAHUAcgBlACAAcgBlAHQAdQByAG4AIABhAG4AIABFAHgAYwBlAGwAIABlAHIAcgBvAHIALAAgAG8AdABoAGUAcgB3AGkAcwBlACAAcgBlAHQAdQByAG4AIAB0AGgAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAByAGUAcwB1AGwAdAAgACgAXwBjAGEAbABjACkAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABfAGkAbgBwAEMAaABrACAAPQAgADAALAAgAF8AYwBhAGwAYwAsACAAUgBTAF8AQwBFAHIAcgAoAF8AaQBuAHAAQwBoAGsAKQApAFwAbgAgACAAIAAgACkAXABuACkAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAVABFAFMAVAAuAEEAYgBvAHUAdAAiACwAIgBUAEUAUwBUAC4AQwBFAHIAcgAiACwAIgBUAEUAUwBUAC4ARgBsAGEAdAB0AGUAbgAiACwAIgBUAEUAUwBUAC4ARgBsAGEAdAB0AGUAbgBfAE0AdQBsAHQAaQBrAGUAeQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgCjACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAGcAYgAiAH0AfQA=</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuAC8AKgAgACAAUgBYAEwAXwBUAGUAeAB0AEIAZQB0AHcAZQBlAG4AIABGAHUAbgBjAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAB2AGUAcgBzAGkAbwBuACAAMQAuADAAOAAgACAAKAAyADMALQBBAHAAcgAtADIAMAAyADUAKQAgAFwAbgAgACAAIAAgACAAIAAgACAAUgAgAFMAaQBsAGsALAAgAFIAWABMACAARABlAHYAZQBsAG8AcABtAGUAbgB0AFwAbgAgACAAIAAgACAAIAAgACAAaAB0AHQAcABzADoALwAvAGcAaQBzAHQALgBnAGkAdABoAHUAYgAuAGMAbwBtAC8AcgAtAHMAaQBsAGsALwBiADMAMwBiADEANgBlADYAMwA0AGUAMQBmAGYANgBhAGEAMAA1ADQAYwBkADYAMQA0ADkAOQA2ADQAZAA4ADAAXABuACoALwBcAG4ALwAqAFwAbgAgACAAIAAgAE4AYQBtAGUAOgAgACAAIAAgACAAIAAgACAAVABlAHgAdABCAGUAdAB3AGUAZQBuACgAKQBcAG4AIAAgACAAIABEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgAgACoALwAvACoAKgBSAGUAdAB1AHIAbgBzACAAdABoAGUAIABjAGgAYQByAGEAYwB0AGUAcgBzACAAZgByAG8AbQAgAGEAIAB0AGUAeAB0ACAAcwB0AHIAaQBuAGcAIABiAGUAdAB3AGUAZQBuACAAYQAgAHMAdABhAHIAdABpAG4AZwAgAGQAZQBsAGkAbQBpAHQAZQByACAAYwBoAGEAcgBhAGMAdABlAHIAKABzACkAIABhAG4AZAAgAGUAbgBkAGkAbgBnACAAZABlAGwAaQBtAGkAdABlAHIAIABjAGgAYQByAGEAYwB0AGUAcgAoAHMAKQAqAC8ALwAqAFwAbgAgACAAIAAgAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACsAIAB0AGUAeAB0ACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA9ACAAKAByAGUAcQB1AGkAcgBlAGQAKQAgAHQAaABlACAAbQBhAGkAbgAgAHQAZQB4AHQAIABzAHQAcgBpAG4AZwAgAHQAbwAgAHMAZQBhAHIAYwBoACAAdwBpAHQAaABpAG4AXABuACAAIAAgACAAIAAgACAAIAArACAAcwB0AGEAcgB0AF8AZABlAGwAaQBtAGkAdABlAHIAIAAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIAB0AGgAZQAgADEAcwB0ACAAZABlAGwAaQBtAGkAdABlAHIAIAB0AG8AIAByAGUAdAB1AHIAbgAgAHQAaABlACAAdABlAHgAdAAgAGEAZgB0AGUAcgBcAG4AIAAgACAAIAAgACAAIAAgACsAIABlAG4AZABfAGQAZQBsAGkAbQBpAHQAZQByACAAIAAgACAAIAA9ACAAKABvAHAAdABpAG8AbgBhAGwAKQAgAHQAaABlACAAMgBuAGQAIABkAGUAbABpAG0AaQB0AGUAcgAgAHQAbwAgAHIAZQB0AHUAcgBuACAAdABoAGUAIAB0AGUAeAB0ACAAYgBlAGYAbwByAGUAXABuACAAIAAgACAAIAAgACAAIAArACAAcwB0AGEAcgB0AF8AaQBuAHMAdABhAG4AYwBlACAAIAAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIAB0AGgAZQAgAGkAbgBzAHQAYQBuAGMAZQAgAG8AZgAgAHQAaABlACAAMQBzAHQAIABkAGUAbABpAG0AaQB0AGUAcgAgAHQAbwAgAGwAbwBvAGsAIABmAG8AcgAgACgAZABlAGYAYQB1AGwAdAAgAD0AIAAxACkAXABuACAAIAAgACAAIAAgACAAIAArACAAZQBuAGQAXwBpAG4AcwB0AGEAbgBjAGUAIAAgACAAIAAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIAB0AGgAZQAgAGkAbgBzAHQAYQBuAGMAZQAgAG8AZgAgAHQAaABlACAAMgBuAGQAIABkAGUAbABpAG0AaQB0AGUAcgAgAHQAbwAgAGwAbwBvAGsAIABmAG8AcgAgACgAZABlAGYAYQB1AGwAdAAgAD0AIAAtADEAKQBcAG4AIAAgACAAIAAgACAAIAAgACsAIABjAGEAcwBlAF8AcwBlAG4AcwBpAHQAaQB2AGUAIAAgACAAIAA9ACAAKABvAHAAdABpAG8AbgBhAGwAKQAgAGMAaABvAG8AcwBlACAAdwBoAGUAdABoAGUAcgAgAHQAaABlACAAdABlAHgAdAAgAHMAZQBhAHIAYwBoACAAaQBzACAAYwBhAHMAZQAgAHMAZQBuAHMAaQB0AGkAdgBlACAAbwByACAAYwBhAHMAZQAgAGkAbgBzAGUAbgBzAGkAdABpAHYAZQAgACgAZABlAGYAYQB1AGwAdAAgAGkAcwAgAGMAYQBzAGUAIABzAGUAbgBzAGkAdABpAHYAZQApAFwAbgAgACAAIAAgACAAIAAgACAAKwAgAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACAAIAAgACAAIAAgAD0AIAAoAG8AcAB0AGkAbwBuAGEAbAApACAAYQAgAHUAcwBlAHIAIABzAHUAcABwAGwAaQBlAGQAIAB2AGEAbAB1AGUAIABvAHIAIABzAHQAcgBpAG4AZwAgAHcAaABpAGMAaAAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAGkAZgAgAHQAaABlACAAcwBlAGEAcgBjAGgAIABkAGUAbABpAG0AaQB0AGUAcgAoAHMAKQAgAGEAcgBlACAAbgBvAHQAIABmAG8AdQBuAGQAXABuACAAIAAgACAARQByAHIAbwByACAAYwBvAGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACMAVgBBAEwAVQBFACEAIAAgACAAIAAgACAAIAAgACAAPQAgAHMAdABhAHIAdABfAGkAbgBzAHQAYQBuAGMAZQAgAGEAbgBkAC8AbwByACAAZQBuAGQAXwBpAG4AcwB0AGEAbgBjAGUAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAaQBuAHYAYQBsAGkAZAAgAC0ALQAgAG4AbwB0ACAAYQAgAG4AbwBuAC0AegBlAHIAbwAgAG4AdQBtAGIAZQByAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIAAgAD0AIABjAGEAcwBlAF8AcwBlAG4AcwBpAHQAaQB2AGUAIABpAG4AcAB1AHQAIABpAHMAIABpAG4AdgBhAGwAaQBkACAALQAtACAAbgBvAHQAIABhACAAbABvAGcAaQBjAGEAbAAvAEIAbwBvAGwAZQBhAG4AIAB2AGEAbAB1AGUAIAAoAFQAUgBVAEUALwBGAEEATABTAEUAKQAgAG8AcgAgAGEAIABuAHUAbQBiAGUAcgAgACgAMQAvADAAKQBcAG4AIAAgACAAIABOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABUAGgAaQBzACAAdgBlAHIAcwBpAG8AbgAgAG8AZgAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAdQBzAGUAcwAgAHQAaABlACAAbgBhAHQAaQB2AGUAIABFAHgAYwBlAGwAIABUAEUAWABUAEEARgBUAEUAUgAoACkAIABhAG4AZAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKAApACAAZgB1AG4AYwB0AGkAbwBuAHMAXABuACAAIAAgACAAIAAgACAAIAAtACAASQBmACAAbgBvACAAZQBuAGQAXwBkAGUAbABpAG0AaQB0AGUAcgAgAGkAcwAgAHMAdQBwAHAAbABpAGUAZAAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAcgBlAHQAdQByAG4AcwAgAHQAaABlACAAdABlAHgAdAAgAGEAZgB0AGUAcgAgAHQAaABlACAAcwB0AGEAcgB0AF8AZABlAGwAaQBtAGkAdABlAHIAIABbAFQARQBYAFQAQQBGAFQARQBSACgAKQAgAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAXQBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABJAGYAIABuAG8AIABzAHQAYQByAHQAXwBkAGUAbABpAG0AaQB0AGUAcgAgAGkAcwAgAHMAdQBwAHAAbABpAGUAZAAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuACAAcgBlAHQAdQByAG4AcwAgAHQAaABlACAAdABlAHgAdAAgAGIAZQBmAG8AcgBlACAAdABoAGUAIABlAG4AZABfAGQAZQBsAGkAbQBpAHQAZQByACAAWwBUAEUAWABUAEIARQBGAE8AUgBFACgAKQAgAGYAdQBuAGMAdABpAG8AbgBhAGwAaQB0AHkAXQBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABJAGYAIABuAGUAaQB0AGgAZQByACAAZABlAGwAaQBtAGkAdABlAHIAIABpAHMAIABzAHUAcABwAGwAaQBlAGQALAAgAHQAaABlACAAZgB1AGwAbAAgAHQAZQB4AHQAIABzAHQAcgBpAG4AZwAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZABcAG4AIAAgACAAIAAgACAAIAAgAC0AIABUAGgAZQAgAGQAZQBsAGkAbQBpAHQAZQByACAAaQBuAHMAdABhAG4AYwBlACAAbgB1AG0AYgBlAHIAcwAgACgAcwB0AGEAcgB0AF8AaQBuAHMAdABhAG4AYwBlACwAIABlAG4AZABfAGkAbgBzAHQAYQBuAGMAZQApACAAcwBoAG8AdQBsAGQAIABiAGUAIABhAG4AIABpAG4AdABlAGcAZQByACAAKAB3AGgAbwBsAGUAIABuAHUAbQBiAGUAcgApACAAZwByAGUAYQB0AGUAcgAgAHQAaABhAG4AIAAwACwAIABhAG4AZAAgAGMAYQBuACAAYgBlACAAcABvAHMAaQB0AGkAdgBlACAAbwByACAAbgBlAGcAYQB0AGkAdgBlAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AIABpAGYAIABhACAAcABvAHMAaQB0AGkAdgBlACAAbgB1AG0AYgBlAHIAIABpAHMAIABwAHIAbwB2AGkAZABlAGQAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAGwAbwBvAGsAcwAgAGYAbwByACAAdABoAGUAIABkAGUAbABpAG0AaQB0AGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHIAdAAgAG8AZgAgAHQAaABlACAAdABlAHgAdAAgAHMAdAByAGkAbgBnAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AIABpAGYAIABhACAAbgBlAGcAYQB0AGkAdgBlACAAbgB1AG0AYgBlAHIAIABpAHMAIABwAHIAbwB2AGkAZABlAGQAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAGwAbwBvAGsAcwAgAGYAbwByACAAdABoAGUAIABkAGUAbABpAG0AaQB0AGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAGUAbgBkACAAbwBmACAAdABoAGUAIAB0AGUAeAB0ACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIAAtACAAVABoAGUAIABjAGEAcwBlAF8AcwBlAG4AcwBpAHQAaQB2AGUAIABwAGEAcgBhAG0AZQB0AGUAcgAgAHMAaABvAHUAbABkACAAYgBlACAAcwB1AHAAcABsAGkAZQBkACAAYQBzACAAZQBpAHQAaABlAHIAIABUAFIAVQBFAC8AMQAgAG8AcgAgAEYAQQBMAFMARQAvADAAOwAgAHQAaABlACAAZABlAGYAYQB1AGwAdAAgAGkAcwAgAFQAUgBVAEUAIAAoAGMAYQBzAGUAIABzAGUAbgBzAGkAdABpAHYAZQAgAHMAZQBhAHIAYwBoACkAXABuACAAIAAgACAAIAAgACAAIAAtACAASQBmACAAdABoAGUAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAbwBtAGkAdAB0AGUAZAAgAG8AcgAgAGIAbABhAG4AawAsACAAdABoAGUAbgAgAGEAIAAjAE4ALwBBACAAYwBvAGQAZQAgAGkAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAGkAZgAgAHQAaABlACAAZABlAGwAaQBtAGkAdABlAHIAIABzAGUAYQByAGMAaAAgAGkAcwAgAGUAbQBwAHQAeQAsACAAbwB0AGgAZQByAHcAaQBzAGUAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAHMAdAByAGkAbgBnACAAaQBzACAAdQBzAGUAZABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAALQAtACAAdABvACAAcgBlAHQAdQByAG4AIABhACAAXAAiAGIAbABhAG4AawBcACIAIAByAGUAcwB1AGwAdAAgAHQAaABlAG4AIAB1AHMAZQAgAGEAIABzAGkAbgBnAGwAZQAgAHMAcABhAGMAZQAgACgAXAAiACAAXAAiACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAC0ALQAgAGkAZgAgAHQAaABlACAAdQBzAGUAcgAgAHMAdQBwAHAAbABpAGUAcwAgAGEAIABsAG8AZwBpAGMAYQBsACAARgBBAEwAUwBFACwAIABhACAAIwBOAC8AQQAgAGUAcgByAG8AcgAgAGMAbwBkAGUAIABpAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB3AGgAZQBuACAAdABoAGUAIABkAGUAbABpAG0AaQB0AGUAcgAgAHMAZQBhAHIAYwBoACAAaQBzACAAZQBtAHAAdAB5AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAtAC0AIABpAGYAIAB0AGgAZQAgAHUAcwBlAHIAIABzAHUAcABwAGwAaQBlAHMAIABhACAAbABvAGcAaQBjAGEAbAAgAFQAUgBVAEUALAAgAHQAaABlACAAbwByAGkAZwBpAG4AYQBsACAAdABlAHgAdAAgAHMAdAByAGkAbgBnACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAdwBoAGUAbgAgAHQAaABlACAAZABlAGwAaQBtAGkAdABlAHIAIABzAGUAYQByAGMAaAAgAGkAcwAgAGUAbQBwAHQAeQBcAG4AKgAvAFwAbgBSAFgATABfAFQAZQB4AHQAQgBlAHQAdwBlAGUAbgAgAD0AIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAC8ALwAgAFAAYQByAGEAbQBlAHQAZQByACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAbgAgACAAIAAgAHQAZQB4AHQALABcAG4AIAAgACAAIABbAHMAdABhAHIAdABfAGQAZQBsAGkAbQBpAHQAZQByAF0ALABcAG4AIAAgACAAIABbAGUAbgBkAF8AZABlAGwAaQBtAGkAdABlAHIAXQAsAFwAbgAgACAAIAAgAFsAcwB0AGEAcgB0AF8AaQBuAHMAdABhAG4AYwBlAF0ALABcAG4AIAAgACAAIABbAGUAbgBkAF8AaQBuAHMAdABhAG4AYwBlAF0ALABcAG4AIAAgACAAIABbAGMAYQBzAGUAXwBzAGUAbgBzAGkAdABpAHYAZQBdACwAXABuACAAIAAgACAAWwBpAGYAXwBuAG8AdABfAGYAbwB1AG4AZABdACwAXABuACAAIAAgACAALwAvACAATQBhAGkAbgAgAGYAdQBuAGMAdABpAG8AbgAgAGIAbwBkAHkALwBjAGEAbABjAHUAbABhAHQAaQBvAG4AcwBcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARABlAGEAbAAgAHcAaQB0AGgAIABbAG8AcAB0AGkAbwBuAGEAbABdACAAcABhAHIAYQBtAGUAdABlAHIAcwAgAGEAbgBkACAAcwBlAHQAIABkAGUAZgBhAHUAbAB0ACAAdgBhAGwAdQBlAHMAXABuACAAIAAgACAAIAAgACAAIABfAGQAZQBsAGkAbQBBACwAIABJAEYAKAAgAE8AUgAoACAASQBTAE8ATQBJAFQAVABFAEQAKABzAHQAYQByAHQAXwBkAGUAbABpAG0AaQB0AGUAcgApACwAIABJAFMAQgBMAEEATgBLACgAcwB0AGEAcgB0AF8AZABlAGwAaQBtAGkAdABlAHIAKQApACwAIABcACIAXAAiACwAIABzAHQAYQByAHQAXwBkAGUAbABpAG0AaQB0AGUAcgApACwAXABuACAAIAAgACAAIAAgACAAIABfAGQAZQBsAGkAbQBCACwAIABJAEYAKAAgAE8AUgAoACAASQBTAE8ATQBJAFQAVABFAEQAKABlAG4AZABfAGQAZQBsAGkAbQBpAHQAZQByACkALAAgAEkAUwBCAEwAQQBOAEsAKABlAG4AZABfAGQAZQBsAGkAbQBpAHQAZQByACkAKQAsACAAXAAiAFwAIgAsACAAZQBuAGQAXwBkAGUAbABpAG0AaQB0AGUAcgApACwAXABuACAAIAAgACAAIAAgACAAIABfAGkAbgBzAHQAQQAsACAASQBGACgAIABPAFIAKAAgAEkAUwBPAE0ASQBUAFQARQBEACgAcwB0AGEAcgB0AF8AaQBuAHMAdABhAG4AYwBlACkALAAgAEkAUwBCAEwAQQBOAEsAKABzAHQAYQByAHQAXwBpAG4AcwB0AGEAbgBjAGUAKQApACwAIAAxACwAIABJAE4AVAAoAHMAdABhAHIAdABfAGkAbgBzAHQAYQBuAGMAZQApACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AaQBuAHMAdABCACwAIABJAEYAKAAgAE8AUgAoACAASQBTAE8ATQBJAFQAVABFAEQAKABlAG4AZABfAGkAbgBzAHQAYQBuAGMAZQApACwAIABJAFMAQgBMAEEATgBLACgAZQBuAGQAXwBpAG4AcwB0AGEAbgBjAGUAKQApACwAIAAtADEALAAgAEkATgBUACgAZQBuAGQAXwBpAG4AcwB0AGEAbgBjAGUAKQApACwAXABuACAAIAAgACAAIAAgACAAIABfAGMAYQBzAGUALAAgAEkARgAoACAASQBTAE8ATQBJAFQAVABFAEQAKABjAGEAcwBlAF8AcwBlAG4AcwBpAHQAaQB2AGUAKQAsACAAMAAsACAASQBGACgAYwBhAHMAZQBfAHMAZQBuAHMAaQB0AGkAdgBlACwAIAAwACwAIAAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgBwAHUAdAAgAGMAaABlAGMAawBpAG4AZwAgAGYAbwByACAAdABoAGUAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBuACAAbwByAGQAZQByACAAdABvACAAcAByAG8AdgBpAGQAZQAgACMATgAvAEEAIAByAGUAcwB1AGwAdAAgAHcAaABlAG4AIABuAG8AIAByAGUAdAB1AHIAbgAgAHMAdAByAGkAbgBnACAAaQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAGEAIAAjAFYAQQBMAFUARQAhACAAUgBlAHMAdQBsAHQAXABuACAAIAAgACAAIAAgACAAIABfAGkAbgBmACwAIABJAEYAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAIABJAFMATwBNAEkAVABUAEUARAAoAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALAAgAEkAUwBCAEwAQQBOAEsAKABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAAgAD0AIABcACIAXAAiACwAIABBAE4ARAAoACAASQBTAEwATwBHAEkAQwBBAEwAKABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAAgAD0AIABGAEEATABTAEUAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AQQAoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAIABJAFMATABPAEcASQBDAEEATAAoAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkALAAgAHQAZQB4AHQALAAgAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABfAGUAbgBkACwAIABJAEYAKAAgAEkAUwBMAE8ARwBJAEMAQQBMACgAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAKQAsACAAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAIAAqACAAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGgAZQBjAGsAIABmAG8AcgAgAGkAbgB2AGEAbABpAGQAIABpAG4AcAB1AHQAIAB2AGEAbAB1AGUAcwAgAC0ALQAgAHIAZQB0AHUAcgBuAHMAIAB2AGEAbAB1AGUAIABvAGYAOgAgADAAIAA9ACAAbgBvACAAaQBuAHAAdQB0ACAAZQByAHIAbwByAHMAOwAgAD4AMAAgAD0AIABpAG4AcAB1AHQAIABlAHIAcgBvAHIAKABzACkAIABpAGQAZQBuAHQAaQBmAGkAZQBkAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAdABoAGkAcwAgAGkAcwAgAHAAbABhAGMAZQBkACAAYQBmAHQAZQByACAAZABlAGEAbABpAG4AZwAgAHcAaQB0AGgAIABvAHAAdABpAG8AbgBhAGwAIABwAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwAgAHMAbwAgAHQAaABhAHQAIABhAG4AIABvAG0AaQB0AHQAZQBkACAAaQBuAHAAdQB0ACAAZABvAGUAcwAgAG4AbwB0ACAAcgBlAGcAaQBzAHQAZQByACAAYQBuACAAaQBuAHAAdQB0ACAAZQByAHIAbwByAFwAbgAgACAAIAAgACAAIAAgACAAXwBpAG4AcABDAGgAawAsACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4ATwBUACgASQBTAE4AVQBNAEIARQBSACgAXwBpAG4AcwB0AEEAKQApACwAIABfAGkAbgBzAHQAQQAgAD0AIAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATgBPAFQAKABJAFMATgBVAE0AQgBFAFIAKABfAGkAbgBzAHQAQgApACkALAAgAF8AaQBuAHMAdABCACAAPQAgADAALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoACAATgBPAFQAKABJAFMATABPAEcASQBDAEEATAAoAF8AYwBhAHMAZQApACkALAAgAE4ATwBUACgASQBTAE4AVQBNAEIARQBSACgAXwBjAGEAcwBlACkAKQApAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADIALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHMAdAByAGkAbgBnACAAdQBzAGkAbgBnACAAVABFAFgAVABBAEYAVABFAFIAKAApACAAYQBuAGQAIABUAEUAWABUAEIARQBGAE8AUgBFACgAKQAgAGYAdQBuAGMAdABpAG8AbgBzAFwAbgAgACAAIAAgACAAIAAgACAAXwBjAGEAbABjACwAIABJAEYAKAAgAE8AUgAoACAAQQBOAEQAKABfAGQAZQBsAGkAbQBBACAAPQAgAFwAIgBcACIALAAgAF8AZABlAGwAaQBtAEIAIAA9ACAAXAAiAFwAIgApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAdABlAHgAdAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEUAWABUAEIARQBGAE8AUgBFACgAIABUAEUAWABUAEEARgBUAEUAUgAoAHQAZQB4AHQALAAgAF8AZABlAGwAaQBtAEEALAAgAF8AaQBuAHMAdABBACwAIABfAGMAYQBzAGUALAAgAF8AZQBuAGQALAAgAF8AaQBuAGYAKQAsACAAXwBkAGUAbABpAG0AQgAsACAAXwBpAG4AcwB0AEIALAAgAF8AYwBhAHMAZQAsACAALAAgAF8AaQBuAGYAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAbwByACAAdABoAGUAIABmAGkAbgBhAGwAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AIABvAHUAdABwAHUAdAAsACAAaQBmACAAdABoAGUAIABhAG4AIABpAG4AcAB1AHQAIABlAHIAcgBvAHIAIABjAGgAZQBjAGsAIABtAGUAcwBzAGEAZwBlAC8AYwBvAGQAZQAgAGkAcwAgAHAAcgBlAHMAZQBuAHQAIAByAGUAdAB1AHIAbgAgAHQAaABhAHQALAAgAG8AdABoAGUAcgB3AGkAcwBlACAAcgBlAHQAdQByAG4AIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAcwB0AHIAaQBuAGcAXABuACAAIAAgACAAIAAgACAAIABfAHIAdABuACwAIABJAEYAKAAgAEEATgBEACgAIABJAFMARQBSAFIATwBSACgAXwBjAGEAbABjACkALAAgAF8AZQBuAGQAIAA9ACAAMQApACwAIAB0AGUAeAB0ACwAIABfAGMAYQBsAGMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKABfAGkAbgBwAEMAaABrACwAIABfAHIAdABuACwAIAAjAFYAQQBMAFUARQAhACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAFIAWABMAF8AVABlAHgAdABCAGUAdAB3AGUAZQBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiAKMAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
